--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case AllergyIntolerance</t>
+    <t>This StructureDefinition contains the maps for VistA PATIENT ALLERGIES (file 120.8) to FHIR AllergyIntolerance</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="396">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -584,7 +584,7 @@
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-clinical</t>
+    <t>http://va.gov/fhir/ValueSet/VFallergyActive</t>
   </si>
   <si>
     <t>ait-1
@@ -615,7 +615,7 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-verification</t>
+    <t>http://va.gov/fhir/ValueSet/VFallergyEnteredInError</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -640,10 +640,7 @@
     <t>Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
   </si>
   <si>
-    <t>Identification of the underlying physiological mechanism for a Reaction Risk.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergy-intolerance-type|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFallergyMechanism</t>
   </si>
   <si>
     <t>code</t>
@@ -677,10 +674,7 @@
     <t>This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
   </si>
   <si>
-    <t>Category of an identified substance associated with allergies or intolerances.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergy-intolerance-category|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFallergySubstanceCategory</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -1238,10 +1232,7 @@
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
   </si>
   <si>
-    <t>Clinical assessment of the severity of a reaction event as a whole, potentially considering multiple different manifestations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/reaction-event-severity|4.0.1</t>
+    <t>http://va.gov/fhir/ValueSet/VFallergySeverity</t>
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (#120.85-14.5)</t>
@@ -4043,11 +4034,9 @@
       <c r="X21" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Y21" t="s" s="2">
+      <c r="Y21" s="2"/>
+      <c r="Z21" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>38</v>
@@ -4080,31 +4069,31 @@
         <v>57</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4126,13 +4115,13 @@
         <v>65</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4160,11 +4149,9 @@
       <c r="X22" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Y22" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>38</v>
@@ -4182,7 +4169,7 @@
         <v>38</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4197,31 +4184,31 @@
         <v>57</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4243,13 +4230,13 @@
         <v>65</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4278,10 +4265,10 @@
         <v>128</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>38</v>
@@ -4299,7 +4286,7 @@
         <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4314,13 +4301,13 @@
         <v>57</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>38</v>
@@ -4331,14 +4318,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4360,13 +4347,13 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4396,7 +4383,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>38</v>
@@ -4414,7 +4401,7 @@
         <v>38</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4429,27 +4416,27 @@
         <v>57</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4561,10 +4548,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4678,10 +4665,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4704,19 +4691,19 @@
         <v>46</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>38</v>
@@ -4765,7 +4752,7 @@
         <v>38</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -4780,13 +4767,13 @@
         <v>57</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>38</v>
@@ -4797,10 +4784,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4826,16 +4813,16 @@
         <v>112</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>38</v>
@@ -4884,7 +4871,7 @@
         <v>38</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -4899,31 +4886,31 @@
         <v>57</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4942,13 +4929,13 @@
         <v>46</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4999,7 +4986,7 @@
         <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>45</v>
@@ -5014,27 +5001,27 @@
         <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5057,13 +5044,13 @@
         <v>38</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5114,7 +5101,7 @@
         <v>38</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5129,10 +5116,10 @@
         <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>38</v>
@@ -5146,10 +5133,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5172,13 +5159,13 @@
         <v>38</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5229,7 +5216,7 @@
         <v>38</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5244,10 +5231,10 @@
         <v>57</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>38</v>
@@ -5261,10 +5248,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5287,13 +5274,13 @@
         <v>38</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5344,7 +5331,7 @@
         <v>38</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -5359,31 +5346,31 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5402,13 +5389,13 @@
         <v>38</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5459,7 +5446,7 @@
         <v>38</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -5474,31 +5461,31 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5517,16 +5504,16 @@
         <v>46</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5576,7 +5563,7 @@
         <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -5591,13 +5578,13 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>38</v>
@@ -5608,10 +5595,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5634,16 +5621,16 @@
         <v>38</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5693,7 +5680,7 @@
         <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -5708,7 +5695,7 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>38</v>
@@ -5725,10 +5712,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5751,16 +5738,16 @@
         <v>38</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5810,7 +5797,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -5825,7 +5812,7 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>38</v>
@@ -5842,10 +5829,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5957,10 +5944,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6074,10 +6061,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6100,16 +6087,16 @@
         <v>46</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6147,7 +6134,7 @@
         <v>38</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
@@ -6157,7 +6144,7 @@
         <v>121</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6172,7 +6159,7 @@
         <v>57</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>38</v>
@@ -6189,13 +6176,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>38</v>
@@ -6220,13 +6207,13 @@
         <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6276,7 +6263,7 @@
         <v>38</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -6291,7 +6278,7 @@
         <v>57</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>38</v>
@@ -6303,15 +6290,15 @@
         <v>38</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6334,13 +6321,13 @@
         <v>46</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6391,7 +6378,7 @@
         <v>38</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -6406,7 +6393,7 @@
         <v>57</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>38</v>
@@ -6415,18 +6402,18 @@
         <v>88</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6449,13 +6436,13 @@
         <v>46</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6506,7 +6493,7 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>45</v>
@@ -6521,7 +6508,7 @@
         <v>57</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>38</v>
@@ -6533,15 +6520,15 @@
         <v>38</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6564,13 +6551,13 @@
         <v>38</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6621,7 +6608,7 @@
         <v>38</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -6636,7 +6623,7 @@
         <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>38</v>
@@ -6653,10 +6640,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6768,10 +6755,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6885,14 +6872,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6914,10 +6901,10 @@
         <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>94</v>
@@ -6972,7 +6959,7 @@
         <v>38</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7004,10 +6991,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7033,13 +7020,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7065,14 +7052,14 @@
         <v>38</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="Y47" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>38</v>
       </c>
@@ -7089,7 +7076,7 @@
         <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7104,7 +7091,7 @@
         <v>57</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>38</v>
@@ -7121,14 +7108,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7150,13 +7137,13 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7186,7 +7173,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>38</v>
@@ -7204,7 +7191,7 @@
         <v>38</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>45</v>
@@ -7219,31 +7206,31 @@
         <v>57</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7265,13 +7252,13 @@
         <v>112</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7321,7 +7308,7 @@
         <v>38</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -7336,7 +7323,7 @@
         <v>57</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>38</v>
@@ -7353,10 +7340,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7379,13 +7366,13 @@
         <v>38</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7436,7 +7423,7 @@
         <v>38</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -7451,13 +7438,13 @@
         <v>57</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>38</v>
@@ -7468,10 +7455,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7497,13 +7484,13 @@
         <v>65</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7531,11 +7518,9 @@
       <c r="X51" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>38</v>
@@ -7553,7 +7538,7 @@
         <v>38</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
@@ -7568,7 +7553,7 @@
         <v>57</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>38</v>
@@ -7580,15 +7565,15 @@
         <v>38</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7614,13 +7599,13 @@
         <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7646,13 +7631,13 @@
         <v>38</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>38</v>
@@ -7670,7 +7655,7 @@
         <v>38</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7685,7 +7670,7 @@
         <v>57</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>38</v>
@@ -7702,10 +7687,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7728,16 +7713,16 @@
         <v>38</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7787,7 +7772,7 @@
         <v>38</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7802,7 +7787,7 @@
         <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>38</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,129 @@
   </si>
   <si>
     <t>constraint</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 v2 Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Allergy
@@ -584,7 +707,7 @@
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergyActive</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergyActive</t>
   </si>
   <si>
     <t>ait-1
@@ -615,7 +738,7 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergyEnteredInError</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergyEnteredInError</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -640,7 +763,7 @@
     <t>Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergyMechanism</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergyMechanism</t>
   </si>
   <si>
     <t>code</t>
@@ -674,7 +797,7 @@
     <t>This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergySubstanceCategory</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergySubstanceCategory</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -1232,7 +1355,7 @@
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFallergySeverity</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFallergySeverity</t>
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (#120.85-14.5)</t>
@@ -1585,17 +1708,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.78515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.55859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1603,6207 +1727,6332 @@
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.42578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="11.4375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.39453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.703125" customWidth="true"/>
+    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="16.3984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="49.1171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="125.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" t="s" s="2">
+      <c r="A1" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" t="s" s="2">
+      <c r="B1" t="s" s="1">
         <v>36</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="C1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="D1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="I1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K1" t="s" s="2">
+      <c r="E1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="F1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="G1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="N1" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="O1" s="2"/>
-      <c r="P1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Z1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="AG1" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH1" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AI1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AJ1" t="s" s="2">
+      <c r="H1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="AK1" t="s" s="2">
+      <c r="I1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="AL1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN1" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AO1" t="s" s="2">
-        <v>38</v>
+      <c r="J1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="K1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="L1" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="M1" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="O1" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="P1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s" s="1">
+        <v>52</v>
+      </c>
+      <c r="S1" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s" s="1">
+        <v>54</v>
+      </c>
+      <c r="U1" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="V1" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="W1" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="X1" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="Y1" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="Z1" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="AA1" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="AB1" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="AC1" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="AD1" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="AE1" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="AF1" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="AG1" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="AH1" t="s" s="1">
+        <v>68</v>
+      </c>
+      <c r="AI1" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="AJ1" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="AK1" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="AM1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="AN1" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="AO1" t="s" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N3" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>62</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>127</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>161</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>38</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>193</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>38</v>
+        <v>223</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>214</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>38</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>234</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>38</v>
+        <v>267</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>116</v>
+        <v>272</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>38</v>
+        <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>38</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>133</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>258</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>38</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>264</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>38</v>
+        <v>304</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>38</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>38</v>
+        <v>324</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>293</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>38</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>38</v>
+        <v>342</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>38</v>
+        <v>343</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>113</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>116</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>317</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>318</v>
+        <v>133</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>319</v>
+        <v>159</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="AD39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>157</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>112</v>
+        <v>358</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>333</v>
+        <v>367</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>340</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>38</v>
+        <v>381</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>112</v>
+        <v>383</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>113</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>114</v>
+        <v>385</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>115</v>
+        <v>382</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>133</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>159</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>163</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>38</v>
+        <v>390</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>360</v>
+        <v>129</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>200</v>
+        <v>401</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>374</v>
+        <v>241</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>38</v>
+        <v>408</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>38</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>38</v>
+        <v>411</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>65</v>
+        <v>319</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>38</v>
+        <v>419</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>384</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>388</v>
+        <v>423</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>391</v>
+        <v>263</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>38</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>38</v>
+        <v>398</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>38</v>
+        <v>430</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>38</v>
+        <v>431</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>313</v>
+        <v>432</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>38</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO53">
+  <autoFilter ref="A1:AO54">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7813,7 +8062,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI53">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,10 +240,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Allergy
@@ -720,10 +720,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
-  </si>
-  <si>
-    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
   </si>
   <si>
     <t>AllergyIntolerance.verificationStatus</t>
@@ -775,10 +775,10 @@
     <t>IAM-9</t>
   </si>
   <si>
+    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (#120.8-17)</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.Mechanism</t>
-  </si>
-  <si>
-    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (#120.8-17)</t>
   </si>
   <si>
     <t>AllergyIntolerance.category</t>
@@ -806,10 +806,10 @@
     <t>AL1-2</t>
   </si>
   <si>
+    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.AllergyType</t>
-  </si>
-  <si>
-    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
   </si>
   <si>
     <t>AllergyIntolerance.criticality</t>
@@ -946,10 +946,10 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
+    <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.AllergicReactant</t>
-  </si>
-  <si>
-    <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient</t>
@@ -1039,6 +1039,9 @@
   </si>
   <si>
     <t>IAM-13</t>
+  </si>
+  <si>
+    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.OriginationDateTime
@@ -1048,9 +1051,6 @@
 Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
-    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.recorder</t>
   </si>
   <si>
@@ -1196,10 +1196,10 @@
     <t>Act.effectiveTime</t>
   </si>
   <si>
+    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
+  </si>
+  <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
-  </si>
-  <si>
-    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.text</t>
@@ -1749,8 +1749,8 @@
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="49.1171875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="125.08984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="49.1171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3750,10 +3750,10 @@
         <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4212,10 +4212,10 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4674,10 +4674,10 @@
         <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5259,10 +5259,10 @@
         <v>304</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5719,10 +5719,10 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>334</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6536,10 +6536,10 @@
         <v>129</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -6766,10 +6766,10 @@
         <v>129</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7464,10 +7464,10 @@
         <v>408</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7811,10 +7811,10 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" hidden="true">

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -647,6 +650,9 @@
     <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID (#null)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.id</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.period</t>
   </si>
   <si>
@@ -723,6 +729,9 @@
     <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.removed</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
@@ -745,6 +754,9 @@
   </si>
   <si>
     <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.type</t>
   </si>
   <si>
     <t>AllergyIntolerance.type</t>
@@ -807,6 +819,9 @@
   </si>
   <si>
     <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.severity</t>
   </si>
   <si>
     <t>Allergy.Allergy.AllergyType</t>
@@ -888,6 +903,9 @@
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (#120.8-2)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.vuid</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.code.id</t>
   </si>
   <si>
@@ -949,6 +967,9 @@
     <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.name</t>
+  </si>
+  <si>
     <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
@@ -1042,6 +1063,9 @@
   </si>
   <si>
     <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.entered</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.OriginationDateTime
@@ -1181,6 +1205,9 @@
     <t>1503: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (#120.8-26 &gt; 120.826-1)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.note.time</t>
   </si>
   <si>
@@ -1197,6 +1224,9 @@
   </si>
   <si>
     <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
@@ -1224,6 +1254,9 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (#120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.reaction</t>
   </si>
   <si>
@@ -1312,6 +1345,9 @@
     <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (#120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.reaction [m]</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.reaction.description</t>
   </si>
   <si>
@@ -1343,6 +1379,9 @@
     <t>AL1-6</t>
   </si>
   <si>
+    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (#120.8-10 &gt; 120.81-3)</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
@@ -1359,6 +1398,9 @@
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (#120.85-14.5)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.comment [m].entered</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -1708,7 +1750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AP54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.78515625" customWidth="true" bestFit="true"/>
@@ -1750,7 +1792,8 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="49.1171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="49.1171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1877,6 +1920,9 @@
       <c r="AO1" t="s" s="1">
         <v>75</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>76</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1887,6172 +1933,6331 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>7</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP2" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP3" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP4" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP5" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP6" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP7" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP8" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP9" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AG10" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP10" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH11" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP14" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>230</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>227</v>
+        <v>238</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>230</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>249</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AA23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AB23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF23" t="s" s="2">
+      <c r="AI23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>260</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH27" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>303</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP31" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>334</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="B41" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="C41" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="AA49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH49" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="S54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO54">
+  <autoFilter ref="A1:AP54">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,7 +647,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID (#null)</t>
+    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.id</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA PATIENT ALLERGIES (file 120.8) to FHIR AllergyIntolerance</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT ALLERGIES (#120.8) to us-core-allergyintolerance</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,10 +243,10 @@
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Virtual Patient Record (VPR)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Allergy
@@ -729,10 +729,10 @@
     <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
   </si>
   <si>
+    <t>Allergy.Allergy.EnteredInErrorFlag</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.removed</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
     <t>AllergyIntolerance.verificationStatus</t>
@@ -821,10 +821,10 @@
     <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
   </si>
   <si>
+    <t>Allergy.Allergy.AllergyType</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.severity</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.AllergyType</t>
   </si>
   <si>
     <t>AllergyIntolerance.criticality</t>
@@ -967,10 +967,10 @@
     <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
   </si>
   <si>
+    <t>Allergy.Allergy.AllergicReactant</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.name</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient</t>
@@ -1063,9 +1063,6 @@
   </si>
   <si>
     <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.entered</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.OriginationDateTime
@@ -1075,6 +1072,9 @@
 Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.entered</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.recorder</t>
   </si>
   <si>
@@ -1226,10 +1226,10 @@
     <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
   </si>
   <si>
+    <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
-  </si>
-  <si>
-    <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.text</t>
@@ -1792,8 +1792,8 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="53.2421875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="49.1171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="49.1171875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="53.2421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3749,7 +3749,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -3844,10 +3844,10 @@
         <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4318,10 +4318,10 @@
         <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4343,7 +4343,7 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
@@ -4436,10 +4436,10 @@
         <v>248</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4461,7 +4461,7 @@
         <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
@@ -4792,10 +4792,10 @@
         <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5177,7 +5177,7 @@
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>80</v>
@@ -5653,7 +5653,7 @@
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>80</v>
@@ -5771,7 +5771,7 @@
         <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -6607,7 +6607,7 @@
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>80</v>
@@ -6702,10 +6702,10 @@
         <v>375</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -6727,7 +6727,7 @@
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>80</v>
@@ -6845,7 +6845,7 @@
         <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
@@ -6938,10 +6938,10 @@
         <v>391</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7654,10 +7654,10 @@
         <v>420</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7799,7 +7799,7 @@
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
@@ -7917,7 +7917,7 @@
         <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8010,10 +8010,10 @@
         <v>438</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="53" hidden="true">

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1380,6 +1380,9 @@
   </si>
   <si>
     <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (#120.8-10 &gt; 120.81-3)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergicReaction.EnteredDateTime</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.severity</t>
@@ -7892,7 +7895,7 @@
         <v>432</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -7900,10 +7903,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7929,13 +7932,13 @@
         <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7965,7 +7968,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -7983,7 +7986,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8007,21 +8010,21 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8047,13 +8050,13 @@
         <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8082,10 +8085,10 @@
         <v>409</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8103,7 +8106,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8118,7 +8121,7 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
@@ -8138,10 +8141,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8167,13 +8170,13 @@
         <v>358</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8223,7 +8226,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1065,11 +1065,7 @@
     <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
   </si>
   <si>
-    <t>Allergy.AllergicReaction.OriginationDateTime
-Allergy.Allergy.OriginationDateTime
-Allergy.AllergyComment.OriginationDateTime
-Allergy.AllergyDrugClass.OriginationDateTime
-Allergy.AllergyDrugIngredient.OriginationDateTime</t>
+    <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.entered</t>
@@ -1795,7 +1791,7 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="49.1171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="53.2421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -238,15 +247,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Allergy
@@ -641,16 +641,16 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.id</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.id</t>
   </si>
   <si>
     <t>AllergyIntolerance.identifier.period</t>
@@ -720,21 +720,21 @@
 ait-2</t>
   </si>
   <si>
+    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+  </si>
+  <si>
+    <t>Allergy.Allergy.EnteredInErrorFlag</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.removed</t>
+  </si>
+  <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
   </si>
   <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.EnteredInErrorFlag</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.removed</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
@@ -750,13 +750,13 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergyEnteredInError</t>
   </si>
   <si>
+    <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.type</t>
+  </si>
+  <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
-  </si>
-  <si>
-    <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.type</t>
   </si>
   <si>
     <t>AllergyIntolerance.type</t>
@@ -778,6 +778,12 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergyMechanism</t>
   </si>
   <si>
+    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (#120.8-17)</t>
+  </si>
+  <si>
+    <t>Allergy.Allergy.Mechanism</t>
+  </si>
+  <si>
     <t>code</t>
   </si>
   <si>
@@ -785,12 +791,6 @@
   </si>
   <si>
     <t>IAM-9</t>
-  </si>
-  <si>
-    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (#120.8-17)</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.Mechanism</t>
   </si>
   <si>
     <t>AllergyIntolerance.category</t>
@@ -812,19 +812,19 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergySubstanceCategory</t>
   </si>
   <si>
+    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
+  </si>
+  <si>
+    <t>Allergy.Allergy.AllergyType</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.severity</t>
+  </si>
+  <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
   </si>
   <si>
     <t>AL1-2</t>
-  </si>
-  <si>
-    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.AllergyType</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.severity</t>
   </si>
   <si>
     <t>AllergyIntolerance.criticality</t>
@@ -879,6 +879,12 @@
   </si>
   <si>
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1186.8</t>
+  </si>
+  <si>
+    <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (#120.8-2)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.vuid</t>
   </si>
   <si>
     <t>substance/product:@@ -900,12 +906,6 @@
     <t>AL1-3 / IAM-3</t>
   </si>
   <si>
-    <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (#120.8-2)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.vuid</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.code.id</t>
   </si>
   <si>
@@ -958,19 +958,19 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
+  </si>
+  <si>
+    <t>Allergy.Allergy.AllergicReactant</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.name</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
-  </si>
-  <si>
-    <t>Allergy.Allergy.AllergicReactant</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.name</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient</t>
@@ -990,6 +990,9 @@
     <t>The patient who has the allergy or intolerance.</t>
   </si>
   <si>
+    <t>248: source value from PATIENT ALLERGIES - PATIENT (#120.8-.01)</t>
+  </si>
+  <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
   </si>
   <si>
@@ -997,9 +1000,6 @@
   </si>
   <si>
     <t>(PID-3)</t>
-  </si>
-  <si>
-    <t>248: source value from PATIENT ALLERGIES - PATIENT (#120.8-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.encounter</t>
@@ -1053,6 +1053,15 @@
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
+    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.entered</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].time</t>
   </si>
   <si>
@@ -1060,15 +1069,6 @@
   </si>
   <si>
     <t>IAM-13</t>
-  </si>
-  <si>
-    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.entered</t>
   </si>
   <si>
     <t>AllergyIntolerance.recorder</t>
@@ -1088,13 +1088,13 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
+    <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (#120.8-5)</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].role</t>
   </si>
   <si>
     <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (#120.8-5)</t>
   </si>
   <si>
     <t>AllergyIntolerance.asserter</t>
@@ -1216,16 +1216,16 @@
     <t>Annotation.time</t>
   </si>
   <si>
+    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
+  </si>
+  <si>
     <t>Act.effectiveTime</t>
-  </si>
-  <si>
-    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.text</t>
@@ -1244,13 +1244,13 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (#120.8-26 &gt; 120.826-2)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (#120.8-26 &gt; 120.826-2)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction</t>
@@ -1335,13 +1335,13 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
+    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (#120.81-.01 &gt; 120.83-)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.reaction [m]</t>
+  </si>
+  <si>
     <t>AL1-5</t>
-  </si>
-  <si>
-    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (#120.81-.01 &gt; 120.83-)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.reaction [m]</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.description</t>
@@ -1372,13 +1372,13 @@
     <t>Record of the date and/or time of the onset of the Reaction.</t>
   </si>
   <si>
+    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (#120.8-10 &gt; 120.81-3)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergicReaction.EnteredDateTime</t>
+  </si>
+  <si>
     <t>AL1-6</t>
-  </si>
-  <si>
-    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (#120.8-10 &gt; 120.81-3)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergicReaction.EnteredDateTime</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.severity</t>
@@ -1787,12 +1787,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="125.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="125.08984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2025,16 +2025,16 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>80</v>
@@ -2623,16 +2623,16 @@
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>80</v>
@@ -2743,16 +2743,16 @@
         <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>80</v>
@@ -2863,16 +2863,16 @@
         <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>80</v>
@@ -2985,16 +2985,16 @@
         <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>80</v>
@@ -3107,22 +3107,22 @@
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3225,16 +3225,16 @@
         <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3345,16 +3345,16 @@
         <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3467,22 +3467,22 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3589,22 +3589,22 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -3711,22 +3711,22 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3949,22 +3949,22 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4069,22 +4069,22 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -4193,16 +4193,16 @@
         <v>227</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4311,16 +4311,16 @@
         <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4429,16 +4429,16 @@
         <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4544,16 +4544,16 @@
         <v>256</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>260</v>
@@ -4661,22 +4661,22 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4782,16 +4782,16 @@
         <v>277</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>281</v>
@@ -4897,16 +4897,16 @@
         <v>80</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -5017,16 +5017,16 @@
         <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -5139,22 +5139,22 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5264,16 +5264,16 @@
         <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>303</v>
@@ -5382,19 +5382,19 @@
         <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5497,19 +5497,19 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5615,19 +5615,19 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5854,16 +5854,16 @@
         <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5971,22 +5971,22 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6091,16 +6091,16 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6211,16 +6211,16 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6329,16 +6329,16 @@
         <v>80</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6449,16 +6449,16 @@
         <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6567,22 +6567,22 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -6689,22 +6689,22 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>376</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -6810,19 +6810,19 @@
         <v>381</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -6931,16 +6931,16 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7043,16 +7043,16 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7161,16 +7161,16 @@
         <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7281,16 +7281,16 @@
         <v>138</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7403,16 +7403,16 @@
         <v>138</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7523,16 +7523,16 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7641,16 +7641,16 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>245</v>
+        <v>419</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>420</v>
+        <v>247</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7761,16 +7761,16 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7879,22 +7879,22 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AO51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7997,22 +7997,22 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8117,16 +8117,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8237,16 +8237,16 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT ALLERGIES (#120.8) to us-core-allergyintolerance</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT ALLERGIES (120.8) to us-core-allergyintolerance</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -720,7 +720,7 @@
 ait-2</t>
   </si>
   <si>
-    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+    <t>536: terminologyMaps using VF_allergyActive on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
   </si>
   <si>
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
@@ -750,7 +750,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergyEnteredInError</t>
   </si>
   <si>
-    <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (#120.8-22)</t>
+    <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.type</t>
@@ -778,7 +778,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergyMechanism</t>
   </si>
   <si>
-    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (#120.8-17)</t>
+    <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (120.8-17)</t>
   </si>
   <si>
     <t>Allergy.Allergy.Mechanism</t>
@@ -812,7 +812,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergySubstanceCategory</t>
   </si>
   <si>
-    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (#120.8-3.1)</t>
+    <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (120.8-3.1)</t>
   </si>
   <si>
     <t>Allergy.Allergy.AllergyType</t>
@@ -881,7 +881,7 @@
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1186.8</t>
   </si>
   <si>
-    <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (#120.8-2)</t>
+    <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.vuid</t>
@@ -958,7 +958,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>245: source value from PATIENT ALLERGIES - REACTANT (#120.8-.02)</t>
+    <t>245: source value from PATIENT ALLERGIES - REACTANT (120.8-.02)</t>
   </si>
   <si>
     <t>Allergy.Allergy.AllergicReactant</t>
@@ -990,7 +990,7 @@
     <t>The patient who has the allergy or intolerance.</t>
   </si>
   <si>
-    <t>248: source value from PATIENT ALLERGIES - PATIENT (#120.8-.01)</t>
+    <t>248: source value from PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
@@ -1053,7 +1053,7 @@
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (#120.8-4)</t>
+    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (120.8-4)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
@@ -1088,7 +1088,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (#120.8-5)</t>
+    <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].role</t>
@@ -1198,7 +1198,7 @@
     <t>authorString</t>
   </si>
   <si>
-    <t>1503: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (#120.8-26 &gt; 120.826-1)</t>
+    <t>1503: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (120.8-26 &gt; 120.826-1)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
@@ -1216,7 +1216,7 @@
     <t>Annotation.time</t>
   </si>
   <si>
-    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (#120.8-26 &gt; 120.826-.01)</t>
+    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (120.8-26 &gt; 120.826-.01)</t>
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
@@ -1244,7 +1244,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (#120.8-26 &gt; 120.826-2)</t>
+    <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
@@ -1335,7 +1335,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (#120.81-.01 &gt; 120.83-)</t>
+    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.reaction [m]</t>
@@ -1372,7 +1372,7 @@
     <t>Record of the date and/or time of the onset of the Reaction.</t>
   </si>
   <si>
-    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (#120.8-10 &gt; 120.81-3)</t>
+    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.EnteredDateTime</t>
@@ -1396,7 +1396,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergySeverity</t>
   </si>
   <si>
-    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (#120.85-14.5)</t>
+    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.comment [m].entered</t>
@@ -1787,7 +1787,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="125.08984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="123.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -3834,7 +3834,7 @@
         <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>202</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1335,7 +1335,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.81-.01 &gt; 120.83-)</t>
+    <t>252: source value from REACTIONS - REACTION &gt; HOSPITAL LOCATION - (120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.reaction [m]</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1335,7 +1335,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from REACTIONS - REACTION &gt; HOSPITAL LOCATION - (120.81-.01 &gt; 120.83-)</t>
+    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.reaction [m]</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="456">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -993,6 +993,9 @@
     <t>248: source value from PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
   </si>
   <si>
+    <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
+  </si>
+  <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
   </si>
   <si>
@@ -1091,6 +1094,9 @@
     <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
   </si>
   <si>
+    <t>Allergy.Allergy.OriginatingStaffIEN</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].role</t>
   </si>
   <si>
@@ -1201,6 +1207,9 @@
     <t>1503: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (120.8-26 &gt; 120.826-1)</t>
   </si>
   <si>
+    <t>Allergy.AllergyComment.EnteringStaffIEN</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
   </si>
   <si>
@@ -1338,6 +1347,9 @@
     <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
+    <t>Allergy.AllergicReaction.ReactionIEN</t>
+  </si>
+  <si>
     <t>GET PATIENT DATA-reaction.reaction [m]</t>
   </si>
   <si>
@@ -1372,7 +1384,7 @@
     <t>Record of the date and/or time of the onset of the Reaction.</t>
   </si>
   <si>
-    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3)</t>
+    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3) case 6 OBSERVED/HISTORICAL = O</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.EnteredDateTime</t>
@@ -1787,7 +1799,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="123.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="138.33984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -5382,27 +5394,27 @@
         <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5425,13 +5437,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5482,7 +5494,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5506,10 +5518,10 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5517,10 +5529,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5543,13 +5555,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5600,7 +5612,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5624,10 +5636,10 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5635,10 +5647,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5661,13 +5673,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5718,7 +5730,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5733,34 +5745,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5779,13 +5791,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5836,7 +5848,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5851,19 +5863,19 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5871,14 +5883,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5897,16 +5909,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5956,7 +5968,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5980,21 +5992,21 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6017,16 +6029,16 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6076,7 +6088,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6100,7 +6112,7 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6111,10 +6123,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6137,16 +6149,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6196,7 +6208,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6220,7 +6232,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6231,10 +6243,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6349,10 +6361,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6469,10 +6481,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6495,16 +6507,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6542,7 +6554,7 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -6552,7 +6564,7 @@
         <v>163</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6576,7 +6588,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6587,13 +6599,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>80</v>
@@ -6618,13 +6630,13 @@
         <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6674,7 +6686,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6689,16 +6701,16 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6709,10 +6721,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6735,13 +6747,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6792,7 +6804,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6807,16 +6819,16 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6827,10 +6839,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6853,13 +6865,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6910,7 +6922,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6925,16 +6937,16 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -6945,10 +6957,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6971,13 +6983,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7028,7 +7040,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7052,7 +7064,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7063,10 +7075,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7181,10 +7193,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7301,14 +7313,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7330,10 +7342,10 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>136</v>
@@ -7388,7 +7400,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7423,10 +7435,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7452,13 +7464,13 @@
         <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7484,13 +7496,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7508,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7532,7 +7544,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7543,14 +7555,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7572,13 +7584,13 @@
         <v>176</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7608,7 +7620,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7626,7 +7638,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -7641,13 +7653,13 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>247</v>
@@ -7656,19 +7668,19 @@
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7690,13 +7702,13 @@
         <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7746,7 +7758,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7770,7 +7782,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7781,10 +7793,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7807,13 +7819,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7864,7 +7876,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7879,30 +7891,30 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7928,13 +7940,13 @@
         <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7964,25 +7976,25 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7997,13 +8009,13 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>268</v>
@@ -8017,10 +8029,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8046,13 +8058,13 @@
         <v>176</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8078,31 +8090,31 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8126,7 +8138,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8137,10 +8149,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8163,16 +8175,16 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8222,7 +8234,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8246,7 +8258,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,6 +485,13 @@
     <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -492,6 +499,15 @@
   </si>
   <si>
     <t>IAM-7</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-IEN</t>
+  </si>
+  <si>
+    <t>va-IEN</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-IEN.id</t>
   </si>
   <si>
     <t>AllergyIntolerance.identifier.id</t>
@@ -513,6 +529,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>AllergyIntolerance.identifier:va-IEN.extension</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.extension</t>
   </si>
   <si>
@@ -526,12 +545,12 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
+    <t>AllergyIntolerance.identifier:va-IEN.use</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.use</t>
   </si>
   <si>
@@ -560,6 +579,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-IEN.type</t>
   </si>
   <si>
     <t>AllergyIntolerance.identifier.type</t>
@@ -596,6 +618,9 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>AllergyIntolerance.identifier:va-IEN.system</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.system</t>
   </si>
   <si>
@@ -611,18 +636,27 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/identifiers/Sta3n&lt;stationNr&gt;/120.8</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
   </si>
   <si>
+    <t>233-1: fixed value = http://va.gov/identifiers/Sta3n&lt;stationNr&gt;/120.8</t>
+  </si>
+  <si>
     <t>II.root or Role.id.root</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
+    <t>AllergyIntolerance.identifier:va-IEN.value</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.value</t>
   </si>
   <si>
@@ -641,7 +675,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
+    <t>233: source value from PATIENT ALLERGIES - IEN (120.8-.001)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.id</t>
@@ -651,6 +685,9 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-IEN.period</t>
   </si>
   <si>
     <t>AllergyIntolerance.identifier.period</t>
@@ -675,6 +712,9 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
+    <t>AllergyIntolerance.identifier:va-IEN.assigner</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.identifier.assigner</t>
   </si>
   <si>
@@ -698,6 +738,48 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW</t>
+  </si>
+  <si>
+    <t>va-CDW</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.use</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.type</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.system</t>
+  </si>
+  <si>
+    <t>http://va.gov/identifiers/CDWSID/cdwwork.allergy.allergy</t>
+  </si>
+  <si>
+    <t>1610-1: fixed value = http://va.gov/identifiers/CDWSID/cdwwork.allergy.allergy</t>
+  </si>
+  <si>
+    <t>1610-1: fixed value from undefined</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.value</t>
+  </si>
+  <si>
+    <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.period</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.identifier:va-CDW.assigner</t>
   </si>
   <si>
     <t>AllergyIntolerance.clinicalStatus</t>
@@ -1354,6 +1436,162 @@
   </si>
   <si>
     <t>AL1-5</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.extension</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.840.1.113883.6.233</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>252-1: fixed value = urn:oid:2.16.840.1.113883.6.233</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>252-2: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.81-.01 &gt; 120.83-99.99)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergicReaction.ReactionIEN
+Dim.Reaction.VUID</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>252-3: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.81-.01 &gt; 120.83-.01)</t>
+  </si>
+  <si>
+    <t>Allergy.AllergicReaction.ReactionIEN
+Dim.Reaction.Reaction</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.reaction.manifestation.text</t>
+  </si>
+  <si>
+    <t>252-4: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.81-.01 &gt; 120.83-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.description</t>
@@ -1761,11 +1999,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP54"/>
+  <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.78515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.3984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.3984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -3092,16 +3330,14 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>144</v>
@@ -3128,23 +3364,25 @@
         <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3162,19 +3400,23 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3222,19 +3464,19 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3246,32 +3488,32 @@
         <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
@@ -3283,17 +3525,15 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3330,43 +3570,43 @@
         <v>80</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3377,46 +3617,44 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3440,43 +3678,43 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
@@ -3488,21 +3726,21 @@
         <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3519,25 +3757,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3562,13 +3800,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3586,7 +3824,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3610,21 +3848,21 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>185</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3647,19 +3885,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3672,43 +3910,43 @@
         <v>80</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3732,21 +3970,21 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3769,18 +4007,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
       </c>
@@ -3789,10 +4029,10 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>80</v>
@@ -3828,7 +4068,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3843,13 +4083,13 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>203</v>
@@ -3866,7 +4106,7 @@
         <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3880,7 +4120,7 @@
         <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
@@ -3889,7 +4129,7 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>207</v>
@@ -3897,7 +4137,9 @@
       <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3910,7 +4152,7 @@
         <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>80</v>
@@ -3946,7 +4188,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3961,30 +4203,30 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4007,17 +4249,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4066,7 +4306,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4090,21 +4330,21 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4118,25 +4358,25 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4162,11 +4402,13 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>80</v>
@@ -4184,7 +4426,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4193,38 +4435,40 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4236,27 +4480,29 @@
         <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4280,11 +4526,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -4302,49 +4550,49 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>152</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4354,26 +4602,24 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4398,11 +4644,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4420,7 +4668,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4432,37 +4680,37 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4472,25 +4720,25 @@
         <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4516,29 +4764,31 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4550,37 +4800,37 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4593,7 +4843,7 @@
         <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
@@ -4602,15 +4852,17 @@
         <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>264</v>
+        <v>173</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4634,13 +4886,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4658,7 +4910,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4682,35 +4934,35 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>270</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
@@ -4719,18 +4971,20 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>185</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4754,11 +5008,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -4776,7 +5032,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4791,30 +5047,30 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4828,25 +5084,29 @@
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4855,10 +5115,10 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>80</v>
@@ -4894,7 +5154,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4906,65 +5166,65 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>80</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4978,7 +5238,7 @@
         <v>80</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>80</v>
@@ -5002,57 +5262,57 @@
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5063,7 +5323,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5075,20 +5335,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>219</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5136,13 +5392,13 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
@@ -5160,21 +5416,21 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>292</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5188,7 +5444,7 @@
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>80</v>
@@ -5197,20 +5453,18 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5258,7 +5512,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5273,38 +5527,38 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>231</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>303</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
@@ -5313,21 +5567,23 @@
         <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5352,13 +5608,11 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5376,45 +5630,45 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5428,24 +5682,26 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>315</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5470,13 +5726,11 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5494,7 +5748,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5503,25 +5757,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5529,14 +5783,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5546,24 +5800,26 @@
         <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5588,13 +5844,11 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5612,7 +5866,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5627,41 +5881,41 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>88</v>
@@ -5670,18 +5924,20 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5706,13 +5962,11 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5730,13 +5984,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5745,34 +5999,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>331</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>332</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>334</v>
+        <v>275</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>335</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5782,24 +6036,26 @@
         <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5824,13 +6080,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -5848,7 +6104,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5863,44 +6119,44 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
@@ -5909,16 +6165,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>347</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5944,13 +6200,11 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -5968,7 +6222,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5983,30 +6237,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>353</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6029,17 +6283,15 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>327</v>
+        <v>159</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>355</v>
+        <v>160</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6088,7 +6340,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>162</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6100,7 +6352,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6112,7 +6364,7 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>358</v>
+        <v>163</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6123,14 +6375,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6149,16 +6401,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>360</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>361</v>
+        <v>134</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>362</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>363</v>
+        <v>136</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6196,19 +6448,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>359</v>
+        <v>169</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6220,7 +6472,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6232,7 +6484,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>364</v>
+        <v>163</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6243,10 +6495,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6257,7 +6509,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -6266,19 +6518,23 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>312</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>155</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
@@ -6326,19 +6582,19 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>157</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6350,55 +6606,57 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>158</v>
+        <v>318</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>160</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6434,71 +6692,71 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>158</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
@@ -6507,17 +6765,15 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6554,20 +6810,22 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>87</v>
@@ -6579,34 +6837,32 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>130</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6618,26 +6874,24 @@
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6686,7 +6940,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6701,30 +6955,30 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6738,22 +6992,22 @@
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6804,7 +7058,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6819,30 +7073,30 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>386</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6850,7 +7104,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6862,16 +7116,16 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6922,10 +7176,10 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>87</v>
@@ -6937,41 +7191,41 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>130</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>88</v>
@@ -6983,13 +7237,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7040,13 +7294,13 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
@@ -7055,19 +7309,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>80</v>
+        <v>368</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7075,14 +7329,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7098,18 +7352,20 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>154</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>155</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7158,7 +7414,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>157</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7170,7 +7426,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7182,32 +7438,32 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>158</v>
+        <v>378</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>80</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7219,16 +7475,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>134</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>160</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7278,19 +7534,19 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7302,7 +7558,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>158</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7313,14 +7569,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7333,26 +7589,24 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7400,7 +7654,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7412,7 +7666,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7424,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>130</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7435,10 +7689,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7461,17 +7715,15 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7496,13 +7748,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>413</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>414</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7520,7 +7772,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>162</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7532,7 +7784,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7544,7 +7796,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>415</v>
+        <v>163</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7555,24 +7807,24 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>417</v>
+        <v>132</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
@@ -7581,16 +7833,16 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>420</v>
+        <v>136</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7616,32 +7868,34 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>169</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>79</v>
@@ -7650,37 +7904,37 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>247</v>
+        <v>163</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7696,19 +7950,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7746,19 +8000,17 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7782,23 +8034,25 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7816,18 +8070,20 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>327</v>
+        <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7876,7 +8132,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7891,30 +8147,30 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>324</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>437</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7934,20 +8190,18 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7972,11 +8226,13 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>442</v>
+        <v>80</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -7994,7 +8250,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8009,30 +8265,30 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>268</v>
+        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>80</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8040,32 +8296,30 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>176</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8090,13 +8344,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>449</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8114,10 +8368,10 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>87</v>
@@ -8129,30 +8383,30 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>80</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8166,7 +8420,7 @@
         <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
@@ -8175,17 +8429,15 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8234,7 +8486,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8258,17 +8510,2535 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y59" s="2"/>
+      <c r="Z59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y73" s="2"/>
+      <c r="Z73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP54">
+  <autoFilter ref="A1:AP75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8278,7 +11048,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,7 +636,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/identifiers/Sta3n&lt;stationNr&gt;/120.8</t>
+    <t>http://va.gov/identifiers/Sta3n$stationNr/120.8</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -645,7 +645,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>233-1: fixed value = http://va.gov/identifiers/Sta3n&lt;stationNr&gt;/120.8</t>
+    <t>233-1: fixed value = http://va.gov/identifiers/Sta3n$stationNr/120.8</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,7 +636,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/identifiers/Sta3n$stationNr/120.8</t>
+    <t>http://va.gov/identifiers/$Sta3n/120.8</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -645,7 +645,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>233-1: fixed value = http://va.gov/identifiers/Sta3n$stationNr/120.8</t>
+    <t>233-1: fixed value = http://va.gov/identifiers/$Sta3n/120.8</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1426,10 +1426,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.81-.01 &gt; 120.83-)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergicReaction.ReactionIEN</t>
+    <t>252: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt;  120.83-)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.reaction [m]</t>
@@ -1519,11 +1516,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>252-2: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.81-.01 &gt; 120.83-99.99)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergicReaction.ReactionIEN
-Dim.Reaction.VUID</t>
+    <t>252-2: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.8-10 &gt; 120.81-.01 &gt;  120.83-99.99)</t>
   </si>
   <si>
     <t>./code</t>
@@ -1547,11 +1540,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>252-3: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.81-.01 &gt; 120.83-.01)</t>
-  </si>
-  <si>
-    <t>Allergy.AllergicReaction.ReactionIEN
-Dim.Reaction.Reaction</t>
+    <t>252-3: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt;  120.83-.01)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -1591,7 +1580,7 @@
     <t>AllergyIntolerance.reaction.manifestation.text</t>
   </si>
   <si>
-    <t>252-4: source value from REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.81-.01 &gt; 120.83-.01)</t>
+    <t>252-4: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt;  120.83-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.description</t>
@@ -2037,7 +2026,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="138.33984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="142.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -9102,10 +9091,10 @@
         <v>449</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>274</v>
@@ -9114,15 +9103,15 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9237,10 +9226,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9357,10 +9346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9479,10 +9468,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9597,10 +9586,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9717,10 +9706,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9746,16 +9735,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9765,46 +9754,46 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9819,30 +9808,30 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9868,13 +9857,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9924,7 +9913,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9948,21 +9937,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9988,14 +9977,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10044,7 +10033,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10059,30 +10048,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10108,14 +10097,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10164,7 +10153,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10179,30 +10168,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10225,19 +10214,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10286,7 +10275,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10310,21 +10299,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10423,10 +10412,10 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
@@ -10443,14 +10432,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10472,13 +10461,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10528,7 +10517,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10552,7 +10541,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10563,10 +10552,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10592,10 +10581,10 @@
         <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10646,7 +10635,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10661,10 +10650,10 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
@@ -10676,15 +10665,15 @@
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10710,13 +10699,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10746,7 +10735,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10764,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10779,13 +10768,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>295</v>
@@ -10799,10 +10788,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10828,13 +10817,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10863,10 +10852,10 @@
         <v>439</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10884,7 +10873,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10908,7 +10897,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10919,10 +10908,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10948,13 +10937,13 @@
         <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11004,7 +10993,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1393,7 +1393,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
+    <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1480,7 +1480,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>252-2: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.8-10 &gt; 120.81-.01 &gt; 120.83-99.99)</t>
+    <t>252-2: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.8-10 &gt; 120.81-.01 &gt; 120.83-99.99)</t>
   </si>
   <si>
     <t>./code</t>
@@ -1504,7 +1504,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>252-3: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
+    <t>252-3: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -1544,7 +1544,7 @@
     <t>AllergyIntolerance.reaction.manifestation.text</t>
   </si>
   <si>
-    <t>252-4: source value from PATIENT ALlERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
+    <t>252-4: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.description</t>
@@ -1987,7 +1987,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="141.97265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Resource.id</t>
+  </si>
+  <si>
+    <t>1974: target not supported</t>
   </si>
   <si>
     <t>AllergyIntolerance.meta</t>
@@ -1363,12 +1366,6 @@
     <t>AllergyIntolerance.reaction.id</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>1974: fixed value = - when ADVERSE REACTION REPORTING - RELATED REACTION &gt; PATIENT ALLERGIES - (120.85-.03 &gt; 120.8-)</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.reaction.extension</t>
   </si>
   <si>
@@ -1641,7 +1638,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFallergySeverity</t>
   </si>
   <si>
-    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5) case 120.85=120.8-.03</t>
+    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
   </si>
   <si>
     <t>GET PATIENT DATA-reaction.comment [m].entered</t>
@@ -2390,7 +2387,7 @@
         <v>80</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>80</v>
@@ -2410,10 +2407,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2436,13 +2433,13 @@
         <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2493,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -2505,7 +2502,7 @@
         <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2528,10 +2525,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2554,16 +2551,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2613,7 +2610,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2625,7 +2622,7 @@
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2648,10 +2645,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2674,16 +2671,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2709,13 +2706,13 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>80</v>
@@ -2733,7 +2730,7 @@
         <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2745,7 +2742,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2768,14 +2765,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2794,16 +2791,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2853,7 +2850,7 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2865,7 +2862,7 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
@@ -2877,7 +2874,7 @@
         <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>80</v>
@@ -2888,14 +2885,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2914,16 +2911,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2973,7 +2970,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2997,7 +2994,7 @@
         <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>80</v>
@@ -3008,14 +3005,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3034,16 +3031,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3093,7 +3090,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3105,7 +3102,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3117,7 +3114,7 @@
         <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>80</v>
@@ -3128,14 +3125,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3154,19 +3151,19 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3215,7 +3212,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3227,7 +3224,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3239,7 +3236,7 @@
         <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>80</v>
@@ -3250,10 +3247,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3276,19 +3273,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3325,17 +3322,17 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3347,7 +3344,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3359,24 +3356,24 @@
         <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
@@ -3398,19 +3395,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3459,7 +3456,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3471,7 +3468,7 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3483,21 +3480,21 @@
         <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3520,13 +3517,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3577,7 +3574,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3601,7 +3598,7 @@
         <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3612,14 +3609,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3638,16 +3635,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3685,19 +3682,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3709,7 +3706,7 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
@@ -3721,7 +3718,7 @@
         <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3732,10 +3729,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3758,19 +3755,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3795,13 +3792,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3819,7 +3816,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3831,7 +3828,7 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>80</v>
@@ -3843,21 +3840,21 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3880,19 +3877,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3917,13 +3914,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3941,7 +3938,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3953,7 +3950,7 @@
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -3965,21 +3962,21 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4002,19 +3999,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4024,10 +4021,10 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>80</v>
@@ -4063,7 +4060,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4075,10 +4072,10 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>80</v>
@@ -4087,21 +4084,21 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4124,16 +4121,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4147,7 +4144,7 @@
         <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>80</v>
@@ -4183,7 +4180,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4195,33 +4192,33 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4244,13 +4241,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4301,7 +4298,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4313,7 +4310,7 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
@@ -4325,21 +4322,21 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4362,16 +4359,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4421,7 +4418,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4433,7 +4430,7 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>80</v>
@@ -4445,24 +4442,24 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4484,19 +4481,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4545,7 +4542,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4557,7 +4554,7 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
@@ -4569,21 +4566,21 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4606,13 +4603,13 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4663,7 +4660,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4687,7 +4684,7 @@
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4698,14 +4695,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4724,16 +4721,16 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4771,19 +4768,19 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4795,7 +4792,7 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -4807,7 +4804,7 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4818,10 +4815,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4844,19 +4841,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4881,13 +4878,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4905,7 +4902,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4917,7 +4914,7 @@
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -4929,21 +4926,21 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4966,19 +4963,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5003,13 +5000,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5027,7 +5024,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5039,7 +5036,7 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5051,21 +5048,21 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5088,19 +5085,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5110,10 +5107,10 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>80</v>
@@ -5149,7 +5146,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5161,33 +5158,33 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5210,16 +5207,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5233,7 +5230,7 @@
         <v>80</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>80</v>
@@ -5269,7 +5266,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5281,33 +5278,33 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5330,13 +5327,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5387,7 +5384,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5399,7 +5396,7 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5411,21 +5408,21 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5448,16 +5445,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5507,7 +5504,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5519,7 +5516,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5531,21 +5528,21 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5568,16 +5565,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5603,11 +5600,11 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5625,7 +5622,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5634,25 +5631,25 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5660,10 +5657,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5686,16 +5683,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5721,11 +5718,11 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5743,34 +5740,34 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5778,14 +5775,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5804,16 +5801,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5839,11 +5836,11 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5861,7 +5858,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5873,37 +5870,37 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5922,16 +5919,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5957,11 +5954,11 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5979,7 +5976,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5991,37 +5988,37 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6040,16 +6037,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6075,13 +6072,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6099,7 +6096,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6111,7 +6108,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -6123,25 +6120,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6160,16 +6157,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6195,11 +6192,11 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6217,7 +6214,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6229,33 +6226,33 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6278,13 +6275,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6335,7 +6332,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6359,7 +6356,7 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6370,14 +6367,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6396,16 +6393,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6443,19 +6440,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6467,7 +6464,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6479,7 +6476,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6490,10 +6487,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6516,19 +6513,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6577,7 +6574,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6589,7 +6586,7 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6601,21 +6598,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6638,19 +6635,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6699,7 +6696,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6711,37 +6708,37 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6760,13 +6757,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6817,7 +6814,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6829,33 +6826,33 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6878,13 +6875,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6935,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6947,7 +6944,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6959,10 +6956,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6970,10 +6967,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6996,13 +6993,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7053,7 +7050,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7065,7 +7062,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7077,10 +7074,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7088,10 +7085,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7114,13 +7111,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7171,7 +7168,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7183,37 +7180,37 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7232,13 +7229,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7289,7 +7286,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7301,22 +7298,22 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7324,14 +7321,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7350,16 +7347,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7409,7 +7406,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7421,7 +7418,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7433,21 +7430,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7470,16 +7467,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7529,7 +7526,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7541,7 +7538,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7553,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7564,10 +7561,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7590,16 +7587,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7649,7 +7646,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7661,7 +7658,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7673,7 +7670,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7684,10 +7681,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7710,13 +7707,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7767,7 +7764,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7791,7 +7788,7 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7802,14 +7799,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7828,16 +7825,16 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7875,19 +7872,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7899,7 +7896,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7911,7 +7908,7 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7922,10 +7919,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7948,16 +7945,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7995,17 +7992,17 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8017,7 +8014,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8029,24 +8026,24 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8068,16 +8065,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8127,7 +8124,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8139,33 +8136,33 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8188,13 +8185,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8245,7 +8242,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8257,33 +8254,33 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8306,13 +8303,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8363,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8375,33 +8372,33 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8424,13 +8421,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8481,7 +8478,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8493,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8505,7 +8502,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8513,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8533,7 +8530,7 @@
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
@@ -8542,13 +8539,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8560,7 +8557,7 @@
         <v>80</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>80</v>
@@ -8599,7 +8596,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8614,7 +8611,7 @@
         <v>80</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>80</v>
@@ -8623,7 +8620,7 @@
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8634,14 +8631,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8660,16 +8657,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8719,7 +8716,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8731,7 +8728,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8743,7 +8740,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8754,14 +8751,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8780,19 +8777,19 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="N57" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8841,7 +8838,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8853,7 +8850,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -8865,7 +8862,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8876,10 +8873,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8902,16 +8899,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8937,55 +8934,55 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z58" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8996,14 +8993,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9022,16 +9019,16 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9057,11 +9054,11 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9079,7 +9076,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9091,33 +9088,33 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9140,13 +9137,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9197,7 +9194,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9221,7 +9218,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9232,14 +9229,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9258,16 +9255,16 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9305,19 +9302,19 @@
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9329,7 +9326,7 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -9341,7 +9338,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9352,10 +9349,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9378,19 +9375,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9439,7 +9436,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9451,7 +9448,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9463,21 +9460,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9500,13 +9497,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9557,7 +9554,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9581,7 +9578,7 @@
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9592,14 +9589,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9618,16 +9615,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9665,19 +9662,19 @@
         <v>80</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9689,7 +9686,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9701,7 +9698,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9712,10 +9709,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9738,19 +9735,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9760,84 +9757,84 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK65" t="s" s="2">
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9860,16 +9857,16 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9919,45 +9916,45 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9980,17 +9977,17 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10039,45 +10036,45 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK67" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK67" t="s" s="2">
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10100,17 +10097,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10159,45 +10156,45 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK68" t="s" s="2">
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10220,19 +10217,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10281,45 +10278,45 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10342,19 +10339,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10403,7 +10400,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10415,10 +10412,10 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10427,25 +10424,25 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10464,16 +10461,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10523,7 +10520,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10535,7 +10532,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10547,7 +10544,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10558,10 +10555,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10584,13 +10581,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10641,7 +10638,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10653,33 +10650,33 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10702,16 +10699,16 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10737,53 +10734,53 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK73" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK73" t="s" s="2">
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="AN73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10794,10 +10791,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10820,16 +10817,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10855,55 +10852,55 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="Z74" t="s" s="2">
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10914,10 +10911,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10940,16 +10937,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10999,7 +10996,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11011,7 +11008,7 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11023,7 +11020,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -302,9 +302,6 @@
   </si>
   <si>
     <t>Resource.id</t>
-  </si>
-  <si>
-    <t>1974: target not supported</t>
   </si>
   <si>
     <t>AllergyIntolerance.meta</t>
@@ -2387,7 +2384,7 @@
         <v>80</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>80</v>
@@ -2407,10 +2404,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2433,13 +2430,13 @@
         <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2490,19 +2487,19 @@
         <v>80</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
@@ -2525,10 +2522,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2551,16 +2548,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2610,7 +2607,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2622,7 +2619,7 @@
         <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -2645,10 +2642,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2671,16 +2668,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2706,32 +2703,32 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2742,7 +2739,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2765,14 +2762,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2791,16 +2788,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2850,31 +2847,31 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>80</v>
@@ -2885,14 +2882,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2911,16 +2908,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2970,7 +2967,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2994,7 +2991,7 @@
         <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>80</v>
@@ -3005,14 +3002,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3031,16 +3028,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3090,7 +3087,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3102,7 +3099,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3114,7 +3111,7 @@
         <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>80</v>
@@ -3125,14 +3122,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3151,19 +3148,19 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3212,7 +3209,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3224,7 +3221,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3236,7 +3233,7 @@
         <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>80</v>
@@ -3247,10 +3244,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3273,19 +3270,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3322,17 +3319,17 @@
         <v>80</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3344,7 +3341,7 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3356,24 +3353,24 @@
         <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>80</v>
@@ -3395,19 +3392,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3456,7 +3453,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3468,7 +3465,7 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3480,21 +3477,21 @@
         <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3517,13 +3514,13 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3574,31 +3571,31 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3609,14 +3606,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3635,16 +3632,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3682,19 +3679,19 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3706,7 +3703,7 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
@@ -3718,7 +3715,7 @@
         <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3729,10 +3726,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3755,19 +3752,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3792,69 +3789,69 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="s" s="2">
+      <c r="AG15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3877,19 +3874,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3914,69 +3911,69 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3999,19 +3996,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4021,84 +4018,84 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="T17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="T17" t="s" s="2">
+      <c r="U17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="U17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4121,16 +4118,16 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4144,81 +4141,81 @@
         <v>80</v>
       </c>
       <c r="T18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="U18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="s" s="2">
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK18" t="s" s="2">
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4241,13 +4238,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4298,45 +4295,45 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4359,16 +4356,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4418,48 +4415,48 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4481,19 +4478,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4542,7 +4539,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4554,7 +4551,7 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
@@ -4566,21 +4563,21 @@
         <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>155</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4603,13 +4600,13 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4660,31 +4657,31 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4695,14 +4692,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4721,16 +4718,16 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4768,19 +4765,19 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC23" t="s" s="2">
+      <c r="AD23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4792,7 +4789,7 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -4804,7 +4801,7 @@
         <v>80</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4815,10 +4812,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4841,19 +4838,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4878,69 +4875,69 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4963,19 +4960,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5000,69 +4997,69 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5085,19 +5082,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5107,84 +5104,84 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5207,16 +5204,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5230,44 +5227,44 @@
         <v>80</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="U27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5278,33 +5275,33 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5327,13 +5324,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5384,45 +5381,45 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5445,16 +5442,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5504,45 +5501,45 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>233</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5565,16 +5562,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5600,56 +5597,56 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK30" t="s" s="2">
+      <c r="AL30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5657,10 +5654,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5683,16 +5680,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5718,56 +5715,56 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AO31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5775,14 +5772,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5801,16 +5798,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5836,71 +5833,71 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5919,16 +5916,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5954,11 +5951,11 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5976,7 +5973,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5988,37 +5985,37 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6037,16 +6034,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6072,73 +6069,73 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AA34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6157,16 +6154,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6192,67 +6189,67 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK35" t="s" s="2">
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6275,13 +6272,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6332,31 +6329,31 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6367,14 +6364,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6393,16 +6390,16 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M37" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6440,19 +6437,19 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC37" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC37" t="s" s="2">
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6464,7 +6461,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6476,7 +6473,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6487,10 +6484,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6513,19 +6510,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6574,7 +6571,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6586,7 +6583,7 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6598,21 +6595,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6635,19 +6632,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6696,49 +6693,49 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6757,13 +6754,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6814,7 +6811,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6826,33 +6823,33 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6875,13 +6872,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6932,7 +6929,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6944,7 +6941,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6956,10 +6953,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6967,10 +6964,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6993,13 +6990,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7050,7 +7047,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7062,7 +7059,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7074,10 +7071,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7085,10 +7082,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7111,13 +7108,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7168,7 +7165,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7180,37 +7177,37 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7229,13 +7226,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7286,7 +7283,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7298,22 +7295,22 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7321,14 +7318,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7347,16 +7344,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7406,7 +7403,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7418,7 +7415,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7430,21 +7427,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7467,16 +7464,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7526,7 +7523,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7538,7 +7535,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7550,7 +7547,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7561,10 +7558,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7587,16 +7584,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7646,7 +7643,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7658,7 +7655,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7670,7 +7667,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7681,10 +7678,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7707,13 +7704,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7764,31 +7761,31 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7799,14 +7796,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7825,16 +7822,16 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M49" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7872,19 +7869,19 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC49" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC49" t="s" s="2">
+      <c r="AD49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7896,7 +7893,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7908,7 +7905,7 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -7919,10 +7916,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7945,16 +7942,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7992,58 +7989,58 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8065,16 +8062,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8124,45 +8121,45 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8185,13 +8182,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8242,45 +8239,45 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK52" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN52" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8303,13 +8300,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8360,45 +8357,45 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK53" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8421,13 +8418,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8478,7 +8475,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8490,7 +8487,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8502,7 +8499,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8513,10 +8510,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8539,13 +8536,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8596,31 +8593,31 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8631,14 +8628,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8657,16 +8654,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M56" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8716,7 +8713,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8728,7 +8725,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8740,7 +8737,7 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8751,14 +8748,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8777,19 +8774,19 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>434</v>
-      </c>
       <c r="N57" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8838,7 +8835,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8850,7 +8847,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -8862,7 +8859,7 @@
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -8873,10 +8870,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8899,16 +8896,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8934,55 +8931,55 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Z58" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8993,14 +8990,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9019,16 +9016,16 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9054,11 +9051,11 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9076,7 +9073,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9088,33 +9085,33 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9137,13 +9134,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9194,31 +9191,31 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9229,14 +9226,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9255,16 +9252,16 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M61" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9302,19 +9299,19 @@
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC61" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC61" t="s" s="2">
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9326,7 +9323,7 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
@@ -9338,7 +9335,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9349,10 +9346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9375,19 +9372,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9436,7 +9433,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9448,7 +9445,7 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
@@ -9460,21 +9457,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9497,13 +9494,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9554,31 +9551,31 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9589,14 +9586,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9615,16 +9612,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M64" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9662,19 +9659,19 @@
         <v>80</v>
       </c>
       <c r="AB64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AC64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AC64" t="s" s="2">
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9686,7 +9683,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9698,7 +9695,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9709,10 +9706,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9735,19 +9732,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9757,84 +9754,84 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9857,16 +9854,16 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9916,45 +9913,45 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9977,17 +9974,17 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10036,45 +10033,45 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK67" t="s" s="2">
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10097,17 +10094,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10156,45 +10153,45 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK68" t="s" s="2">
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>490</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10217,19 +10214,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10278,45 +10275,45 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10339,19 +10336,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10400,7 +10397,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10412,10 +10409,10 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10424,25 +10421,25 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10461,16 +10458,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10520,7 +10517,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10532,7 +10529,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10544,7 +10541,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10555,10 +10552,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10581,13 +10578,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10638,7 +10635,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10650,33 +10647,33 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>513</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10699,16 +10696,16 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10734,53 +10731,53 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK73" t="s" s="2">
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AN73" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10791,10 +10788,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10817,16 +10814,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10852,55 +10849,55 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="Z74" t="s" s="2">
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10911,10 +10908,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10937,16 +10934,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10996,7 +10993,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11008,7 +11005,7 @@
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11020,7 +11017,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,9 +678,6 @@
     <t>233: source value from PATIENT ALLERGIES - IEN (120.8-.001)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.id</t>
-  </si>
-  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -808,9 +805,6 @@
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.removed</t>
-  </si>
-  <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
   </si>
   <si>
@@ -833,9 +827,6 @@
   </si>
   <si>
     <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.type</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -898,9 +889,6 @@
   </si>
   <si>
     <t>Allergy.Allergy.AllergyType</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.severity</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -964,9 +952,6 @@
   </si>
   <si>
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.vuid</t>
   </si>
   <si>
     <t>substance/product:@@ -1046,9 +1031,6 @@
     <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.name</t>
-  </si>
-  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -1144,9 +1126,6 @@
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.entered</t>
-  </si>
-  <si>
     <t>.participation[typeCode=AUT].time</t>
   </si>
   <si>
@@ -1292,9 +1271,6 @@
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.note.time</t>
   </si>
   <si>
@@ -1311,9 +1287,6 @@
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1338,9 +1311,6 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
-  </si>
-  <si>
     <t>Act.text</t>
   </si>
   <si>
@@ -1429,9 +1399,6 @@
     <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.reaction [m]</t>
-  </si>
-  <si>
     <t>AL1-5</t>
   </si>
   <si>
@@ -1636,9 +1603,6 @@
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.comment [m].entered</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -2028,7 +1992,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="49.1171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -4198,24 +4162,24 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4238,13 +4202,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4295,7 +4259,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4319,21 +4283,21 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4356,16 +4320,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4415,7 +4379,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4439,24 +4403,24 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4574,7 +4538,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>158</v>
@@ -4692,7 +4656,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>165</v>
@@ -4812,7 +4776,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>171</v>
@@ -4934,7 +4898,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>182</v>
@@ -5056,7 +5020,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>194</v>
@@ -5104,7 +5068,7 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>200</v>
@@ -5158,10 +5122,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5178,7 +5142,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -5278,30 +5242,30 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5324,13 +5288,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5381,7 +5345,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5405,21 +5369,21 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5442,16 +5406,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5501,7 +5465,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5525,21 +5489,21 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5565,13 +5529,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5601,52 +5565,52 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5654,10 +5618,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5683,13 +5647,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5719,7 +5683,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5737,7 +5701,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5746,25 +5710,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5772,14 +5736,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5801,13 +5765,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5837,7 +5801,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5855,7 +5819,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5870,34 +5834,34 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5919,13 +5883,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5955,7 +5919,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5973,7 +5937,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5988,34 +5952,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6037,13 +6001,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6072,10 +6036,10 @@
         <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6093,7 +6057,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6117,25 +6081,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6157,13 +6121,13 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6193,7 +6157,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6211,7 +6175,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6226,30 +6190,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6364,10 +6328,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6484,10 +6448,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6510,19 +6474,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6571,7 +6535,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6595,21 +6559,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6635,16 +6599,16 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6693,7 +6657,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6708,34 +6672,34 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>328</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6754,13 +6718,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6811,7 +6775,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6826,30 +6790,30 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6872,13 +6836,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6929,7 +6893,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6953,10 +6917,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6964,10 +6928,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6990,13 +6954,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7047,7 +7011,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7071,10 +7035,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7082,10 +7046,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7108,13 +7072,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7165,7 +7129,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7180,34 +7144,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7226,13 +7190,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7283,7 +7247,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7298,19 +7262,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7318,14 +7282,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7344,16 +7308,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7403,7 +7367,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7427,21 +7391,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7464,16 +7428,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7523,7 +7487,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7547,7 +7511,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7558,10 +7522,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7584,16 +7548,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7643,7 +7607,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7667,7 +7631,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7678,10 +7642,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7796,10 +7760,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7916,10 +7880,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7942,16 +7906,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7989,7 +7953,7 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7999,7 +7963,7 @@
         <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8023,7 +7987,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8034,13 +7998,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8065,13 +8029,13 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8121,7 +8085,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8136,16 +8100,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8156,10 +8120,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8182,13 +8146,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8239,7 +8203,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8254,16 +8218,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8274,10 +8238,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8300,13 +8264,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8357,7 +8321,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8372,16 +8336,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8392,10 +8356,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8418,13 +8382,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8475,7 +8439,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8499,7 +8463,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8510,10 +8474,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8628,10 +8592,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8748,14 +8712,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8777,10 +8741,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8835,7 +8799,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8870,10 +8834,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8899,13 +8863,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8931,13 +8895,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8955,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8979,7 +8943,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8990,14 +8954,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9019,13 +8983,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9055,7 +9019,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9073,7 +9037,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9088,30 +9052,30 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9226,10 +9190,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9346,10 +9310,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9372,19 +9336,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9433,7 +9397,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9457,21 +9421,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9586,10 +9550,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9706,10 +9670,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9735,16 +9699,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9754,7 +9718,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9793,7 +9757,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9808,7 +9772,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -9817,21 +9781,21 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9857,13 +9821,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9913,7 +9877,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9937,21 +9901,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9977,14 +9941,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10033,7 +9997,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10048,7 +10012,7 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
@@ -10057,21 +10021,21 @@
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10097,14 +10061,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10153,7 +10117,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10168,7 +10132,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -10177,21 +10141,21 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10214,19 +10178,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10275,7 +10239,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10299,21 +10263,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10339,16 +10303,16 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10397,7 +10361,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10412,7 +10376,7 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10421,25 +10385,25 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10461,13 +10425,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10517,7 +10481,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10541,7 +10505,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10552,10 +10516,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10578,13 +10542,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10635,7 +10599,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10650,30 +10614,30 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10699,13 +10663,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10735,7 +10699,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10753,7 +10717,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10768,16 +10732,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>519</v>
+        <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10752,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10817,13 +10781,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10849,13 +10813,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10873,7 +10837,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10897,7 +10861,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10908,10 +10872,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10934,16 +10898,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10993,7 +10957,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11017,7 +10981,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,6 +678,9 @@
     <t>233: source value from PATIENT ALLERGIES - IEN (120.8-.001)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.id</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -805,6 +808,9 @@
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.removed</t>
+  </si>
+  <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
   </si>
   <si>
@@ -827,6 +833,9 @@
   </si>
   <si>
     <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.type</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -889,6 +898,9 @@
   </si>
   <si>
     <t>Allergy.Allergy.AllergyType</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.severity</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -952,6 +964,9 @@
   </si>
   <si>
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.vuid</t>
   </si>
   <si>
     <t>substance/product:@@ -1031,6 +1046,9 @@
     <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.name</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
@@ -1126,6 +1144,9 @@
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.entered</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].time</t>
   </si>
   <si>
@@ -1271,6 +1292,9 @@
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.note.time</t>
   </si>
   <si>
@@ -1287,6 +1311,9 @@
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1311,6 +1338,9 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
+  </si>
+  <si>
     <t>Act.text</t>
   </si>
   <si>
@@ -1399,6 +1429,9 @@
     <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
+    <t>GET PATIENT DATA-reaction.reaction [m]</t>
+  </si>
+  <si>
     <t>AL1-5</t>
   </si>
   <si>
@@ -1603,6 +1636,9 @@
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
+  </si>
+  <si>
+    <t>GET PATIENT DATA-reaction.comment [m].entered</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -1992,7 +2028,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="49.1171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -4162,24 +4198,24 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4202,13 +4238,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4259,7 +4295,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4283,21 +4319,21 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4320,16 +4356,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4379,7 +4415,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4403,24 +4439,24 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4538,7 +4574,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>158</v>
@@ -4656,7 +4692,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>165</v>
@@ -4776,7 +4812,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>171</v>
@@ -4898,7 +4934,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>182</v>
@@ -5020,7 +5056,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>194</v>
@@ -5068,7 +5104,7 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>200</v>
@@ -5122,10 +5158,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5142,7 +5178,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -5242,30 +5278,30 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5288,13 +5324,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5345,7 +5381,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5369,21 +5405,21 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5406,16 +5442,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5465,7 +5501,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5489,21 +5525,21 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5529,13 +5565,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5565,7 +5601,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5583,7 +5619,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5592,25 +5628,25 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5618,10 +5654,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5647,13 +5683,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5683,7 +5719,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5701,7 +5737,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5710,25 +5746,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5736,14 +5772,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5765,13 +5801,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5801,7 +5837,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5819,7 +5855,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5834,34 +5870,34 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5883,13 +5919,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5919,7 +5955,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5937,7 +5973,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5952,34 +5988,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6001,13 +6037,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6036,10 +6072,10 @@
         <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6057,7 +6093,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6081,25 +6117,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6121,13 +6157,13 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6157,7 +6193,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6175,7 +6211,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6190,30 +6226,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6328,10 +6364,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6448,10 +6484,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6474,19 +6510,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6535,7 +6571,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6559,21 +6595,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6599,16 +6635,16 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6657,7 +6693,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6672,34 +6708,34 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6718,13 +6754,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6775,7 +6811,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6790,30 +6826,30 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6836,13 +6872,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6893,7 +6929,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6917,10 +6953,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6928,10 +6964,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6954,13 +6990,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7011,7 +7047,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7035,10 +7071,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7046,10 +7082,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7072,13 +7108,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7129,7 +7165,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7144,34 +7180,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7190,13 +7226,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7247,7 +7283,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7262,19 +7298,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7282,14 +7318,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7308,16 +7344,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7367,7 +7403,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7391,21 +7427,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7428,16 +7464,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7487,7 +7523,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7511,7 +7547,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7522,10 +7558,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7548,16 +7584,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7607,7 +7643,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7631,7 +7667,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7642,10 +7678,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7760,10 +7796,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7880,10 +7916,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7906,16 +7942,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7953,7 +7989,7 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -7963,7 +7999,7 @@
         <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7987,7 +8023,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7998,13 +8034,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8029,13 +8065,13 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8085,7 +8121,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8100,16 +8136,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8120,10 +8156,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8146,13 +8182,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8203,7 +8239,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8218,16 +8254,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8238,10 +8274,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8264,13 +8300,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8321,7 +8357,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8336,16 +8372,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8356,10 +8392,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8382,13 +8418,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8439,7 +8475,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8463,7 +8499,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8474,10 +8510,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8592,10 +8628,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8712,14 +8748,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8741,10 +8777,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8799,7 +8835,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8834,10 +8870,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8863,13 +8899,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8895,13 +8931,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8919,7 +8955,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8943,7 +8979,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8954,14 +8990,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8983,13 +9019,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9019,7 +9055,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9037,7 +9073,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9052,30 +9088,30 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9190,10 +9226,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9310,10 +9346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9336,19 +9372,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9397,7 +9433,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9421,21 +9457,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9550,10 +9586,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9670,10 +9706,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9699,16 +9735,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9718,7 +9754,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9757,7 +9793,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9772,7 +9808,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -9781,21 +9817,21 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9821,13 +9857,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9877,7 +9913,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9901,21 +9937,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>462</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9941,14 +9977,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -9997,7 +10033,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10012,7 +10048,7 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
@@ -10021,21 +10057,21 @@
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10061,14 +10097,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10117,7 +10153,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10132,7 +10168,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
@@ -10141,21 +10177,21 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10178,19 +10214,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10239,7 +10275,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10263,21 +10299,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10303,16 +10339,16 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10361,7 +10397,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10376,7 +10412,7 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
@@ -10385,25 +10421,25 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10425,13 +10461,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10481,7 +10517,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10505,7 +10541,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10516,10 +10552,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10542,13 +10578,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10599,7 +10635,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10614,30 +10650,30 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>501</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10663,13 +10699,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10699,7 +10735,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10717,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10732,16 +10768,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>80</v>
+        <v>519</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10752,10 +10788,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10781,13 +10817,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10813,13 +10849,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10837,7 +10873,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10861,7 +10897,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10872,10 +10908,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10898,16 +10934,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10957,7 +10993,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10981,7 +11017,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,7 +795,7 @@
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFallergyActive</t>
+    <t>http://va.gov/fhir/ValueSet/allergyActive</t>
   </si>
   <si>
     <t>ait-1
@@ -829,7 +829,7 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFallergyEnteredInError</t>
+    <t>http://va.gov/fhir/ValueSet/allergyEnteredInError</t>
   </si>
   <si>
     <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
@@ -857,7 +857,7 @@
     <t>Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFallergyMechanism</t>
+    <t>http://va.gov/fhir/ValueSet/allergyMechanism</t>
   </si>
   <si>
     <t>531: terminologyMaps using VF_allergyMechanism on PATIENT ALLERGIES - MECHANISM (120.8-17)</t>
@@ -891,7 +891,7 @@
     <t>This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFallergySubstanceCategory</t>
+    <t>http://va.gov/fhir/ValueSet/allergySubstanceCategory</t>
   </si>
   <si>
     <t>556: terminologyMaps using VF_allergySubstanceCategory on PATIENT ALLERGIES - ALLERGY TYPE (120.8-3.1)</t>
@@ -1632,7 +1632,7 @@
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFallergySeverity</t>
+    <t>http://va.gov/fhir/ValueSet/allergySeverity</t>
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,9 +678,6 @@
     <t>233: source value from PATIENT ALLERGIES - IEN (120.8-.001)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.id</t>
-  </si>
-  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
   </si>
   <si>
@@ -808,7 +805,7 @@
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.removed</t>
+    <t>reaction.removed</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
@@ -833,9 +830,6 @@
   </si>
   <si>
     <t>537: terminologyMaps using VF_allergyEnteredInError on PATIENT ALLERGIES - ENTERED IN ERROR (120.8-22)</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.type</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
@@ -866,6 +860,9 @@
     <t>Allergy.Allergy.Mechanism</t>
   </si>
   <si>
+    <t>reaction.mechanism</t>
+  </si>
+  <si>
     <t>code</t>
   </si>
   <si>
@@ -900,7 +897,7 @@
     <t>Allergy.Allergy.AllergyType</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.severity</t>
+    <t>reaction.type</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -966,7 +963,7 @@
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.vuid</t>
+    <t>reaction.localCode,reaction.vuid</t>
   </si>
   <si>
     <t>substance/product:@@ -1046,7 +1043,7 @@
     <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.name</t>
+    <t>reaction.name</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1078,6 +1075,9 @@
     <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
   </si>
   <si>
+    <t>reaction.drugClass [m],reaction.drugIngredient [m],reaction.reaction [m]</t>
+  </si>
+  <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
   </si>
   <si>
@@ -1144,7 +1144,7 @@
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.entered</t>
+    <t>reaction.entered</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].time</t>
@@ -1292,7 +1292,7 @@
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.comment [m].commentText</t>
+    <t>reaction.comment [m]</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.time</t>
@@ -1311,9 +1311,6 @@
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
-  </si>
-  <si>
-    <t>GET PATIENT DATA-reaction.comment [m].enteredBy</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1338,9 +1335,6 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.drugIngredient [m]</t>
-  </si>
-  <si>
     <t>Act.text</t>
   </si>
   <si>
@@ -1429,7 +1423,7 @@
     <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.reaction [m]</t>
+    <t>reaction.reaction [m]</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1638,7 +1632,7 @@
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
   </si>
   <si>
-    <t>GET PATIENT DATA-reaction.comment [m].entered</t>
+    <t>reaction.severity</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -2028,7 +2022,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="53.2421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="68.1953125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -4198,24 +4192,24 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4238,13 +4232,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4295,7 +4289,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4319,21 +4313,21 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4356,16 +4350,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4415,7 +4409,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4439,24 +4433,24 @@
         <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4574,7 +4568,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>158</v>
@@ -4692,7 +4686,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>165</v>
@@ -4812,7 +4806,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>171</v>
@@ -4934,7 +4928,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>182</v>
@@ -5056,7 +5050,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>194</v>
@@ -5104,7 +5098,7 @@
         <v>80</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>200</v>
@@ -5158,10 +5152,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -5178,7 +5172,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -5278,30 +5272,30 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5324,13 +5318,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5381,7 +5375,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5405,21 +5399,21 @@
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5442,16 +5436,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5501,7 +5495,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5525,21 +5519,21 @@
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5565,13 +5559,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5601,52 +5595,52 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5654,10 +5648,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5683,13 +5677,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5719,7 +5713,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5737,7 +5731,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5746,25 +5740,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AO31" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5772,14 +5766,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5801,13 +5795,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5837,7 +5831,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5855,7 +5849,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5870,34 +5864,34 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5919,13 +5913,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5955,7 +5949,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5973,7 +5967,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5988,34 +5982,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6037,13 +6031,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6072,11 +6066,11 @@
         <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6093,7 +6087,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6117,25 +6111,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6157,13 +6151,13 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6193,7 +6187,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6211,7 +6205,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6226,30 +6220,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6364,10 +6358,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6484,10 +6478,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6510,19 +6504,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6571,7 +6565,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6595,21 +6589,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6635,16 +6629,16 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6693,7 +6687,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6708,34 +6702,34 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6754,13 +6748,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6811,7 +6805,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6826,13 +6820,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>338</v>
@@ -8260,10 +8254,10 @@
         <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8274,10 +8268,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8300,13 +8294,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8357,7 +8351,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8372,16 +8366,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8392,10 +8386,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8418,13 +8412,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8475,7 +8469,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8499,7 +8493,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8510,10 +8504,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8628,10 +8622,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8748,14 +8742,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8777,10 +8771,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8835,7 +8829,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8870,10 +8864,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8899,13 +8893,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8931,14 +8925,14 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Y58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8955,7 +8949,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8979,7 +8973,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8990,14 +8984,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9019,13 +9013,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9055,7 +9049,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9073,7 +9067,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9088,30 +9082,30 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9226,10 +9220,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9346,10 +9340,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9372,19 +9366,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9433,7 +9427,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9457,21 +9451,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9586,10 +9580,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9706,10 +9700,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9735,16 +9729,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9754,7 +9748,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9793,7 +9787,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9808,30 +9802,30 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9857,13 +9851,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9913,7 +9907,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9937,21 +9931,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9977,14 +9971,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10033,7 +10027,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10048,30 +10042,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10097,14 +10091,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10153,7 +10147,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10168,30 +10162,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10214,19 +10208,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10275,7 +10269,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10299,21 +10293,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10339,16 +10333,16 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10397,7 +10391,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10412,34 +10406,34 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10461,13 +10455,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10517,7 +10511,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10541,7 +10535,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10552,10 +10546,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10581,10 +10575,10 @@
         <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10635,7 +10629,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10650,13 +10644,13 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>448</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>351</v>
@@ -10665,15 +10659,15 @@
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10699,13 +10693,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10735,7 +10729,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10753,7 +10747,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10768,16 +10762,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10782,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10817,13 +10811,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10849,13 +10843,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10873,7 +10867,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10897,7 +10891,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10908,10 +10902,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10937,13 +10931,13 @@
         <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10993,7 +10987,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -963,7 +963,7 @@
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
-    <t>reaction.localCode,reaction.vuid</t>
+    <t>reaction.drugIngredient [m]</t>
   </si>
   <si>
     <t>substance/product:@@ -1630,9 +1630,6 @@
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
-  </si>
-  <si>
-    <t>reaction.severity</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -10768,7 +10765,7 @@
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>517</v>
+        <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>294</v>
@@ -10782,10 +10779,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10811,13 +10808,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10846,11 +10843,11 @@
         <v>437</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
       </c>
@@ -10867,7 +10864,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10891,7 +10888,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10902,10 +10899,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10931,13 +10928,13 @@
         <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10987,7 +10984,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -805,7 +805,7 @@
     <t>Allergy.Allergy.EnteredInErrorFlag</t>
   </si>
   <si>
-    <t>reaction.removed</t>
+    <t>Allergy.Status</t>
   </si>
   <si>
     <t>Observation ACT .inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
@@ -860,7 +860,7 @@
     <t>Allergy.Allergy.Mechanism</t>
   </si>
   <si>
-    <t>reaction.mechanism</t>
+    <t>Allergy.AllergyExtension.Mechanism</t>
   </si>
   <si>
     <t>code</t>
@@ -897,7 +897,7 @@
     <t>Allergy.Allergy.AllergyType</t>
   </si>
   <si>
-    <t>reaction.type</t>
+    <t>Allergy.AllergyCategory</t>
   </si>
   <si>
     <t>value &lt; IntoleranceValue (Agent)</t>
@@ -963,7 +963,7 @@
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
-    <t>reaction.drugIngredient [m]</t>
+    <t>Allergy.AllergyExtension.DrugProducts</t>
   </si>
   <si>
     <t>substance/product:@@ -1043,7 +1043,7 @@
     <t>Allergy.Allergy.AllergicReactant</t>
   </si>
   <si>
-    <t>reaction.name</t>
+    <t>Allergy.FreeTextAllergy</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1075,7 +1075,7 @@
     <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
   </si>
   <si>
-    <t>reaction.drugClass [m],reaction.drugIngredient [m],reaction.reaction [m]</t>
+    <t>Allergy.ATCCode</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
@@ -1144,9 +1144,6 @@
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
   </si>
   <si>
-    <t>reaction.entered</t>
-  </si>
-  <si>
     <t>.participation[typeCode=AUT].time</t>
   </si>
   <si>
@@ -1179,6 +1176,9 @@
     <t>Allergy.Allergy.OriginatingStaffIEN</t>
   </si>
   <si>
+    <t>Allergy.EnteredBy</t>
+  </si>
+  <si>
     <t>.participation[typeCode=AUT].role</t>
   </si>
   <si>
@@ -1292,7 +1292,8 @@
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
   </si>
   <si>
-    <t>reaction.comment [m]</t>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments
+Allergy.VA.Comment.EnteredBy</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.time</t>
@@ -1311,6 +1312,9 @@
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
+  </si>
+  <si>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1335,6 +1339,10 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments
+Allergy.VA.Comment.CommentText</t>
+  </si>
+  <si>
     <t>Act.text</t>
   </si>
   <si>
@@ -1423,7 +1431,7 @@
     <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
-    <t>reaction.reaction [m]</t>
+    <t>Allergy.Reaction,Allergy.AllergyExtension.Reactions</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1611,6 +1619,10 @@
     <t>Allergy.AllergicReaction.EnteredDateTime</t>
   </si>
   <si>
+    <t>Allergy.Reaction,Allergy.AllergyExtension.Reactions
+Allergy.Reaction.Extension,Allergy.ReactionExtension.EnteredOn</t>
+  </si>
+  <si>
     <t>AL1-6</t>
   </si>
   <si>
@@ -1630,6 +1642,9 @@
   </si>
   <si>
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
+  </si>
+  <si>
+    <t>Allergy.Severity,Allergy.VA.AllergyObservation.Severity</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -2019,7 +2034,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.1953125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="76.2421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>
@@ -7177,28 +7192,28 @@
         <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7217,13 +7232,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7274,7 +7289,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7289,13 +7304,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>370</v>
@@ -8251,10 +8266,10 @@
         <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8265,10 +8280,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8291,13 +8306,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8348,7 +8363,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8363,16 +8378,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8383,10 +8398,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8409,13 +8424,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8466,7 +8481,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8490,7 +8505,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8501,10 +8516,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8619,10 +8634,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8739,14 +8754,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8768,10 +8783,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8826,7 +8841,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8861,10 +8876,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8890,13 +8905,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8922,13 +8937,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8946,7 +8961,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8970,7 +8985,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8981,14 +8996,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9010,13 +9025,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9046,7 +9061,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9064,7 +9079,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9079,13 +9094,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>273</v>
@@ -9094,15 +9109,15 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9217,10 +9232,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9337,10 +9352,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9459,10 +9474,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9577,10 +9592,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9697,10 +9712,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9726,16 +9741,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9745,7 +9760,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9784,7 +9799,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9799,7 +9814,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -9808,21 +9823,21 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9848,13 +9863,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9904,7 +9919,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9928,21 +9943,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9968,14 +9983,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10024,7 +10039,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10039,30 +10054,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10088,14 +10103,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10144,7 +10159,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10159,30 +10174,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10205,19 +10220,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10266,7 +10281,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10290,21 +10305,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10403,13 +10418,13 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>328</v>
@@ -10423,14 +10438,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10452,13 +10467,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10508,7 +10523,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10532,7 +10547,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10543,10 +10558,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10572,10 +10587,10 @@
         <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10626,7 +10641,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10641,13 +10656,13 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>448</v>
+        <v>512</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>351</v>
@@ -10656,15 +10671,15 @@
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10690,13 +10705,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10726,7 +10741,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10744,7 +10759,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10759,13 +10774,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>294</v>
@@ -10779,10 +10794,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10808,13 +10823,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10840,31 +10855,31 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10888,7 +10903,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10899,10 +10914,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10928,13 +10943,13 @@
         <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10984,7 +10999,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -860,7 +860,7 @@
     <t>Allergy.Allergy.Mechanism</t>
   </si>
   <si>
-    <t>Allergy.AllergyExtension.Mechanism</t>
+    <t>Allergy.Extension[AllergyExtension].Mechanism</t>
   </si>
   <si>
     <t>code</t>
@@ -963,7 +963,7 @@
     <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
-    <t>Allergy.AllergyExtension.DrugProducts</t>
+    <t>Allergy.Extension[AllergyExtension].DrugProducts</t>
   </si>
   <si>
     <t>substance/product:@@ -1292,8 +1292,8 @@
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
   </si>
   <si>
-    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments
-Allergy.VA.Comment.EnteredBy</t>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.Extension[AllergyExtension].Comments
+Allergy.Comment[VA.Comment].EnteredBy</t>
   </si>
   <si>
     <t>AllergyIntolerance.note.time</t>
@@ -1314,7 +1314,7 @@
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
   </si>
   <si>
-    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments</t>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.Extension[AllergyExtension].Comments</t>
   </si>
   <si>
     <t>Act.effectiveTime</t>
@@ -1339,8 +1339,8 @@
     <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
-    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.AllergyExtension.Comments
-Allergy.VA.Comment.CommentText</t>
+    <t>Allergy.Comments,Allergy.InactiveComments,Allergy.Extension[AllergyExtension].Comments
+Allergy.Comment[VA.Comment].CommentText</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -1431,7 +1431,7 @@
     <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
-    <t>Allergy.Reaction,Allergy.AllergyExtension.Reactions</t>
+    <t>Allergy.Reaction,Allergy.Extension[AllergyExtension].Reactions</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1619,8 +1619,8 @@
     <t>Allergy.AllergicReaction.EnteredDateTime</t>
   </si>
   <si>
-    <t>Allergy.Reaction,Allergy.AllergyExtension.Reactions
-Allergy.Reaction.Extension,Allergy.ReactionExtension.EnteredOn</t>
+    <t>Allergy.Reaction,Allergy.Extension[AllergyExtension].Reactions
+Allergy.Reaction.Extension,Allergy.Extension[ReactionExtension].EnteredOn</t>
   </si>
   <si>
     <t>AL1-6</t>
@@ -1644,7 +1644,7 @@
     <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
   </si>
   <si>
-    <t>Allergy.Severity,Allergy.VA.AllergyObservation.Severity</t>
+    <t>Allergy.Severity,Allergy.AllergyObservation[VA.AllergyObservation].Severity</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.exposureRoute</t>
@@ -2034,7 +2034,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="76.2421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="86.671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="45.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT ALLERGIES (120.8) to us-core-allergyintolerance</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT ALLERGIES (120.8) to us-core-allergyintolerance.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1073,9 +1073,6 @@
   </si>
   <si>
     <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
-  </si>
-  <si>
-    <t>Allergy.ATCCode</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
@@ -6838,24 +6835,24 @@
         <v>336</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6878,13 +6875,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6935,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6959,10 +6956,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6970,10 +6967,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6996,13 +6993,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7053,7 +7050,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7077,10 +7074,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7088,10 +7085,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7114,13 +7111,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7171,7 +7168,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7186,34 +7183,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7232,13 +7229,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7289,7 +7286,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7304,19 +7301,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7324,14 +7321,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7350,16 +7347,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7409,7 +7406,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7433,21 +7430,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>380</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7470,16 +7467,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7529,7 +7526,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7553,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7564,10 +7561,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7590,16 +7587,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7649,7 +7646,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7673,7 +7670,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7684,10 +7681,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7802,10 +7799,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7922,10 +7919,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7948,16 +7945,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7995,7 +7992,7 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8005,7 +8002,7 @@
         <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8029,7 +8026,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8040,13 +8037,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8071,13 +8068,13 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8127,7 +8124,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8142,16 +8139,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8162,10 +8159,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8188,13 +8185,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8245,7 +8242,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8260,16 +8257,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8280,10 +8277,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8306,13 +8303,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8363,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8378,16 +8375,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8398,10 +8395,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8424,13 +8421,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8481,7 +8478,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8505,7 +8502,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8513,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8634,10 +8631,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8754,14 +8751,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8783,10 +8780,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8841,7 +8838,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8876,10 +8873,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8905,13 +8902,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8937,14 +8934,14 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Y58" t="s" s="2">
+      <c r="Z58" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8961,7 +8958,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8985,7 +8982,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8996,14 +8993,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9025,13 +9022,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9061,7 +9058,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9079,7 +9076,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9094,13 +9091,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>273</v>
@@ -9109,15 +9106,15 @@
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9232,10 +9229,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9352,10 +9349,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9474,10 +9471,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9592,10 +9589,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9712,10 +9709,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9741,16 +9738,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9760,46 +9757,46 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9814,30 +9811,30 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9863,13 +9860,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9919,7 +9916,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9943,21 +9940,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9983,14 +9980,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10039,7 +10036,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10054,30 +10051,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10103,14 +10100,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10159,7 +10156,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10174,30 +10171,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10220,19 +10217,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10281,7 +10278,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10305,21 +10302,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>498</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10418,13 +10415,13 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>328</v>
@@ -10438,14 +10435,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10467,13 +10464,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10523,7 +10520,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10547,7 +10544,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10558,10 +10555,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10584,13 +10581,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10641,7 +10638,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10656,30 +10653,30 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>513</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10705,13 +10702,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10741,7 +10738,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10759,7 +10756,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10774,13 +10771,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>294</v>
@@ -10794,10 +10791,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10823,13 +10820,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10855,14 +10852,14 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
       </c>
@@ -10879,7 +10876,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10903,7 +10900,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10914,10 +10911,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10940,16 +10937,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10999,7 +10996,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11023,7 +11020,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,7 +485,7 @@
     <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -675,7 +675,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>233: source value from PATIENT ALLERGIES - IEN (120.8-.001)</t>
+    <t>233: source value based on PATIENT ALLERGIES - IEN (120.8-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -768,6 +768,9 @@
   </si>
   <si>
     <t>AllergyIntolerance.identifier:va-CDW.value</t>
+  </si>
+  <si>
+    <t>1610: source value based on CDW.cdwwork.allergy.allergy.AllergySID</t>
   </si>
   <si>
     <t>1610: source value from CDW.cdwwork.allergy.allergy.AllergySID</t>
@@ -960,7 +963,7 @@
     <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1186.8</t>
   </si>
   <si>
-    <t>1505: source value from PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
+    <t>1505: source value based on PATIENT ALLERGIES - DRUG INGREDIENTS (120.8-2)</t>
   </si>
   <si>
     <t>Allergy.Extension[AllergyExtension].DrugProducts</t>
@@ -1037,7 +1040,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>245: source value from PATIENT ALLERGIES - REACTANT (120.8-.02)</t>
+    <t>245: source value based on PATIENT ALLERGIES - REACTANT (120.8-.02)</t>
   </si>
   <si>
     <t>Allergy.Allergy.AllergicReactant</t>
@@ -1069,7 +1072,7 @@
     <t>The patient who has the allergy or intolerance.</t>
   </si>
   <si>
-    <t>248: source value from PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
+    <t>248: source value based on PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
@@ -1135,7 +1138,7 @@
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
-    <t>1224: source value from PATIENT ALLERGIES - ORIGINATION DATE/TIME (120.8-4)</t>
+    <t>1224: source value based on PATIENT ALLERGIES - ORIGINATION DATE/TIME (120.8-4)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.OriginationDateTime,Allergy.Allergy.OriginationDateTime,Allergy.AllergyComment.OriginationDateTime,Allergy.AllergyDrugClass.OriginationDateTime,Allergy.AllergyDrugIngredient.OriginationDateTime</t>
@@ -1167,7 +1170,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>251: source value from PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
+    <t>251: source value based on PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
   </si>
   <si>
     <t>Allergy.Allergy.OriginatingStaffIEN</t>
@@ -1283,7 +1286,7 @@
     <t>authorString</t>
   </si>
   <si>
-    <t>1503: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (120.8-26 &gt; 120.826-1)</t>
+    <t>1503: source value based on PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - USER ENTERING (120.8-26 &gt; 120.826-1)</t>
   </si>
   <si>
     <t>Allergy.AllergyComment.EnteringStaffIEN</t>
@@ -1305,7 +1308,7 @@
     <t>Annotation.time</t>
   </si>
   <si>
-    <t>1502: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (120.8-26 &gt; 120.826-.01)</t>
+    <t>1502: source value based on PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - DATE/TIME COMMENT ENTERED (120.8-26 &gt; 120.826-.01)</t>
   </si>
   <si>
     <t>Allergy.AllergyComment.CommentEnteredDateTime</t>
@@ -1333,7 +1336,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1504: source value from PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
+    <t>1504: source value based on PATIENT ALLERGIES - COMMENTS &gt; COMMENTS - COMMENTS (120.8-26 &gt; 120.826-2)</t>
   </si>
   <si>
     <t>Allergy.Comments,Allergy.InactiveComments,Allergy.Extension[AllergyExtension].Comments
@@ -1425,7 +1428,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>252: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
+    <t>252: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS (120.8-10 &gt; 120.81-.01 &gt; 120.83-)</t>
   </si>
   <si>
     <t>Allergy.Reaction,Allergy.Extension[AllergyExtension].Reactions</t>
@@ -1515,7 +1518,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>252-2: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.8-10 &gt; 120.81-.01 &gt; 120.83-99.99)</t>
+    <t>252-2: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - VUID (120.8-10 &gt; 120.81-.01 &gt; 120.83-99.99)</t>
   </si>
   <si>
     <t>./code</t>
@@ -1539,7 +1542,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>252-3: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
+    <t>252-3: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
   </si>
   <si>
     <t>CV.displayName</t>
@@ -1579,7 +1582,7 @@
     <t>AllergyIntolerance.reaction.manifestation.text</t>
   </si>
   <si>
-    <t>252-4: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
+    <t>252-4: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - REACTION &gt; SIGN/SYMPTOMS - NAME (120.8-10 &gt; 120.81-.01 &gt; 120.83-.01)</t>
   </si>
   <si>
     <t>AllergyIntolerance.reaction.description</t>
@@ -1610,7 +1613,11 @@
     <t>Record of the date and/or time of the onset of the Reaction.</t>
   </si>
   <si>
-    <t>1652: source value from PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3) case 6 OBSERVED/HISTORICAL = O</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ai-18-1652:If 6 OBSERVED/HISTORICAL = O then source value from (120.8-10 &gt; 120.81-3) {null}</t>
+  </si>
+  <si>
+    <t>1652: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3) if 6 OBSERVED/HISTORICAL = O</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.EnteredDateTime</t>
@@ -2029,7 +2036,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="142.484375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="146.578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="86.671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -5284,7 +5291,7 @@
         <v>243</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5301,7 +5308,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>216</v>
@@ -5419,7 +5426,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>224</v>
@@ -5539,10 +5546,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5568,13 +5575,13 @@
         <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5604,7 +5611,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5622,7 +5629,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5631,25 +5638,25 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5657,10 +5664,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5686,13 +5693,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5722,7 +5729,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5740,7 +5747,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5749,25 +5756,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5775,14 +5782,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5804,13 +5811,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5840,7 +5847,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5858,7 +5865,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5873,34 +5880,34 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5922,13 +5929,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5958,7 +5965,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5976,7 +5983,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5991,34 +5998,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6040,13 +6047,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6075,10 +6082,10 @@
         <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6096,7 +6103,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6120,25 +6127,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6160,13 +6167,13 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6196,7 +6203,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6214,7 +6221,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6229,30 +6236,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6367,10 +6374,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6487,10 +6494,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6513,19 +6520,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6574,7 +6581,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6598,21 +6605,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6638,16 +6645,16 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6696,7 +6703,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6711,34 +6718,34 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6757,13 +6764,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6814,7 +6821,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6829,30 +6836,30 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6875,13 +6882,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6932,7 +6939,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6956,10 +6963,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6967,10 +6974,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6993,13 +7000,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7050,7 +7057,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7074,10 +7081,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7085,10 +7092,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7111,13 +7118,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7168,7 +7175,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7183,34 +7190,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7229,13 +7236,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7286,7 +7293,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7301,19 +7308,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7321,14 +7328,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7347,16 +7354,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7406,7 +7413,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7430,21 +7437,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7467,16 +7474,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7526,7 +7533,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7550,7 +7557,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7561,10 +7568,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7587,16 +7594,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7646,7 +7653,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7670,7 +7677,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7681,10 +7688,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7799,10 +7806,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7919,10 +7926,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7945,16 +7952,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7992,7 +7999,7 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8002,7 +8009,7 @@
         <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8026,7 +8033,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8037,13 +8044,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8068,13 +8075,13 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8124,7 +8131,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8139,16 +8146,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8159,10 +8166,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8185,13 +8192,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8242,7 +8249,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8257,16 +8264,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8277,10 +8284,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8303,13 +8310,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8360,7 +8367,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8375,16 +8382,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8395,10 +8402,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8421,13 +8428,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8478,7 +8485,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8502,7 +8509,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8513,10 +8520,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8631,10 +8638,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8751,14 +8758,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8780,10 +8787,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8838,7 +8845,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8873,10 +8880,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8902,13 +8909,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8934,13 +8941,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8958,7 +8965,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8982,7 +8989,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -8993,14 +9000,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9022,13 +9029,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9058,7 +9065,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9076,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9091,30 +9098,30 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9229,10 +9236,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9349,10 +9356,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9375,19 +9382,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9436,7 +9443,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9460,21 +9467,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9589,10 +9596,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9709,10 +9716,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9738,16 +9745,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9757,7 +9764,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9796,7 +9803,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9811,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -9820,21 +9827,21 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9860,13 +9867,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9916,7 +9923,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9940,21 +9947,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9980,14 +9987,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10036,7 +10043,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10051,30 +10058,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10100,14 +10107,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10156,7 +10163,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10171,30 +10178,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10217,19 +10224,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10278,7 +10285,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10302,21 +10309,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10342,16 +10349,16 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10400,7 +10407,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10415,34 +10422,34 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10464,13 +10471,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10520,7 +10527,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10544,7 +10551,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10555,10 +10562,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10581,13 +10588,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10638,7 +10645,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10650,33 +10657,33 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>510</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10702,13 +10709,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10738,7 +10745,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10756,7 +10763,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10771,16 +10778,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10791,10 +10798,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10820,13 +10827,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10852,13 +10859,13 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10876,7 +10883,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10900,7 +10907,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10911,10 +10918,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10937,16 +10944,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10996,7 +11003,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11020,7 +11027,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -795,6 +795,9 @@
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
+    <t>see mapping [VF_allergyActive](ConceptMap-VF-allergyActive.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/allergyActive</t>
   </si>
   <si>
@@ -829,6 +832,9 @@
     <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
+    <t>see mapping [VF_allergyEnteredInError](ConceptMap-VF-allergyEnteredInError.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/allergyEnteredInError</t>
   </si>
   <si>
@@ -854,6 +860,9 @@
     <t>Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
   </si>
   <si>
+    <t>see mapping [VF_allergyMechanism](ConceptMap-VF-allergyMechanism.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/allergyMechanism</t>
   </si>
   <si>
@@ -889,6 +898,9 @@
   </si>
   <si>
     <t>This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_allergySubstanceCategory](ConceptMap-VF-allergySubstanceCategory.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/allergySubstanceCategory</t>
@@ -1640,6 +1652,9 @@
   </si>
   <si>
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_allergySeverity](ConceptMap-VF-allergySeverity.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/allergySeverity</t>
@@ -5609,9 +5624,11 @@
       <c r="X30" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y30" s="2"/>
+      <c r="Y30" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5638,25 +5655,25 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5664,10 +5681,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5693,13 +5710,13 @@
         <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5727,9 +5744,11 @@
       <c r="X31" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y31" s="2"/>
+      <c r="Y31" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5747,7 +5766,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5756,25 +5775,25 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5782,14 +5801,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5811,13 +5830,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5845,9 +5864,11 @@
       <c r="X32" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y32" s="2"/>
+      <c r="Y32" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5865,7 +5886,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5880,34 +5901,34 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5929,13 +5950,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5963,9 +5984,11 @@
       <c r="X33" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y33" s="2"/>
+      <c r="Y33" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5983,7 +6006,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5998,34 +6021,34 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6047,13 +6070,13 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6082,10 +6105,10 @@
         <v>176</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6103,7 +6126,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6127,25 +6150,25 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6167,13 +6190,13 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6203,7 +6226,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -6221,7 +6244,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6236,30 +6259,30 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6374,10 +6397,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6494,10 +6517,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6520,19 +6543,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6581,7 +6604,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6605,21 +6628,21 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6645,16 +6668,16 @@
         <v>159</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6703,7 +6726,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6718,34 +6741,34 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6764,13 +6787,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6821,7 +6844,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -6836,30 +6859,30 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6882,13 +6905,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6939,7 +6962,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6963,10 +6986,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6974,10 +6997,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7000,13 +7023,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7057,7 +7080,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7081,10 +7104,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7092,10 +7115,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7118,13 +7141,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7175,7 +7198,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7190,34 +7213,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7236,13 +7259,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7293,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7308,19 +7331,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7328,14 +7351,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7354,16 +7377,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7413,7 +7436,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7437,21 +7460,21 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7474,16 +7497,16 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7533,7 +7556,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7557,7 +7580,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7568,10 +7591,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7594,16 +7617,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7653,7 +7676,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7677,7 +7700,7 @@
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7688,10 +7711,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7806,10 +7829,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7926,10 +7949,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7952,16 +7975,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7999,7 +8022,7 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8009,7 +8032,7 @@
         <v>151</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8033,7 +8056,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8044,13 +8067,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -8075,13 +8098,13 @@
         <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8131,7 +8154,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8146,16 +8169,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8166,10 +8189,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8192,13 +8215,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8249,7 +8272,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8264,16 +8287,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8284,10 +8307,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8310,13 +8333,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8367,7 +8390,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8382,16 +8405,16 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8402,10 +8425,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8428,13 +8451,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8485,7 +8508,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8509,7 +8532,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8520,10 +8543,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8638,10 +8661,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8758,14 +8781,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8787,10 +8810,10 @@
         <v>133</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>136</v>
@@ -8845,7 +8868,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8880,10 +8903,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8909,13 +8932,13 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8941,31 +8964,31 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8989,7 +9012,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>80</v>
@@ -9000,14 +9023,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9029,13 +9052,13 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9065,7 +9088,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9083,7 +9106,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>87</v>
@@ -9098,30 +9121,30 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9236,10 +9259,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9356,10 +9379,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9382,19 +9405,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9443,7 +9466,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9467,21 +9490,21 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9596,10 +9619,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9716,10 +9739,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9745,16 +9768,16 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9764,7 +9787,7 @@
         <v>80</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>80</v>
@@ -9803,7 +9826,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9818,7 +9841,7 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -9827,21 +9850,21 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9867,13 +9890,13 @@
         <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9923,7 +9946,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9947,21 +9970,21 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9987,14 +10010,14 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10043,7 +10066,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10058,30 +10081,30 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10107,14 +10130,14 @@
         <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10163,7 +10186,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10178,30 +10201,30 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10224,19 +10247,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10285,7 +10308,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10309,21 +10332,21 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10349,16 +10372,16 @@
         <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10407,7 +10430,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10422,34 +10445,34 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10471,13 +10494,13 @@
         <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10527,7 +10550,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10551,7 +10574,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10562,10 +10585,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10588,13 +10611,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10645,7 +10668,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10657,33 +10680,33 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10709,13 +10732,13 @@
         <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10743,27 +10766,29 @@
       <c r="X73" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Y73" s="2"/>
+      <c r="Y73" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="Z73" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10778,16 +10803,16 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10798,10 +10823,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10827,13 +10852,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10859,31 +10884,31 @@
         <v>80</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="Z74" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10907,7 +10932,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10918,10 +10943,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10944,16 +10969,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11003,7 +11028,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11027,7 +11052,7 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1074,7 +1074,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1084,7 +1084,7 @@
     <t>The patient who has the allergy or intolerance.</t>
   </si>
   <si>
-    <t>248: source value based on PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
+    <t>248: reference based on PATIENT ALLERGIES - PATIENT (120.8-.01)</t>
   </si>
   <si>
     <t>Allergy.AllergicReaction.PatientIEN,Allergy.Allergy.PatientIEN,Allergy.AllergyComment.PatientIEN,Allergy.AllergyDrugClass.PatientIEN,Allergy.AllergyDrugIngredient.PatientIEN</t>
@@ -1172,7 +1172,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1182,7 +1182,7 @@
     <t>Individual who recorded the record and takes responsibility for its content.</t>
   </si>
   <si>
-    <t>251: source value based on PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
+    <t>251: reference based on PATIENT ALLERGIES - ORIGINATOR (120.8-5)</t>
   </si>
   <si>
     <t>Allergy.Allergy.OriginatingStaffIEN</t>
@@ -1626,7 +1626,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ai-18-1652:If 6 OBSERVED/HISTORICAL = O then source value from (120.8-10 &gt; 120.81-3) {null}</t>
+ai-18-1652:If 6 OBSERVED/HISTORICAL = O then source value from (120.8-10 &gt; 120.81-3) {true}</t>
   </si>
   <si>
     <t>1652: source value based on PATIENT ALLERGIES - REACTIONS &gt; REACTIONS - DATE ENTERED (120.8-10 &gt; 120.81-3) if 6 OBSERVED/HISTORICAL = O</t>
@@ -2026,7 +2026,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.67578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,7 +1660,11 @@
     <t>http://va.gov/fhir/ValueSet/allergySeverity</t>
   </si>
   <si>
-    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5)</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ai-18-557:If ADVERSE REACTION REPORTING – RELATED REACTION (120.85-.03) == PATIENT ALLERGIES (120.8) then terminologyMaps (120.85-14.5) using VF_allergySeverity {true}</t>
+  </si>
+  <si>
+    <t>557: terminologyMaps using VF_allergySeverity on ADVERSE REACTION REPORTING - SEVERITY (120.85-14.5) if ADVERSE REACTION REPORTING – RELATED REACTION (120.85-.03) == PATIENT ALLERGIES (120.8)</t>
   </si>
   <si>
     <t>Allergy.Severity,Allergy.AllergyObservation[VA.AllergyObservation].Severity</t>
@@ -2051,7 +2055,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="146.578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="196.62109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="209.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="86.671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
@@ -10800,16 +10804,16 @@
         <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>525</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>299</v>
@@ -10823,10 +10827,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10852,13 +10856,13 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10887,10 +10891,10 @@
         <v>443</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>80</v>
@@ -10908,7 +10912,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10932,7 +10936,7 @@
         <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -10943,10 +10947,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10972,13 +10976,13 @@
         <v>391</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11028,7 +11032,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-AllergyIntolerance.xlsx
+++ b/docs/StructureDefinition-AllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
